--- a/Excel/4_1_ManureManagement_Feedlot_WIP_v06.xlsx
+++ b/Excel/4_1_ManureManagement_Feedlot_WIP_v06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A90FEF-9F28-457C-90CF-81B4A73353FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC810A61-9943-4FB5-84C0-E96B0885B8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="0" windowWidth="28980" windowHeight="17385" firstSheet="3" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="30" yWindow="0" windowWidth="28980" windowHeight="17385" firstSheet="3" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>

--- a/Excel/4_1_ManureManagement_Feedlot_WIP_v06.xlsx
+++ b/Excel/4_1_ManureManagement_Feedlot_WIP_v06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC810A61-9943-4FB5-84C0-E96B0885B8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC71F06-70D8-4656-887A-FA5137FC36ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="0" windowWidth="28980" windowHeight="17385" firstSheet="3" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="12645" firstSheet="8" activeTab="9" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -22,11 +22,14 @@
     <sheet name="4.1.1.5-6 Atmos Deposition" sheetId="82" r:id="rId7"/>
     <sheet name="4.1.1.9 Manure applied to soils" sheetId="81" r:id="rId8"/>
     <sheet name="Constants - Feedlot" sheetId="79" r:id="rId9"/>
-    <sheet name="Constants - Common" sheetId="97" r:id="rId10"/>
+    <sheet name="Constants - Common" sheetId="98" r:id="rId10"/>
     <sheet name="Constants - Livestock" sheetId="43" r:id="rId11"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId12"/>
     <sheet name="Tab template" sheetId="74" r:id="rId13"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId14"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -42,9 +45,13 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
+    <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayFunctionName">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
@@ -54,6 +61,9 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -135,6 +145,11 @@
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.8.1")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Title">_xlfn.LAMBDA("Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Unit">_xlfn.LAMBDA("fraction")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Source">_xlfn.LAMBDA("")</definedName>
@@ -477,7 +492,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="358">
   <si>
     <t>Home</t>
   </si>
@@ -1763,6 +1778,48 @@
       </rPr>
       <t xml:space="preserve"> Manure that is directly applied to soil after stage 1 is not included in Atmospheric Deposition calculations</t>
     </r>
+  </si>
+  <si>
+    <t>MAT (ºC)</t>
+  </si>
+  <si>
+    <t>Anaerobic lagoon</t>
+  </si>
+  <si>
+    <t>Digester / covered lagoons</t>
+  </si>
+  <si>
+    <t>Liquid systems</t>
+  </si>
+  <si>
+    <t>Daily spread</t>
+  </si>
+  <si>
+    <t>Composting (passive windrow)</t>
+  </si>
+  <si>
+    <t>Solid storage</t>
+  </si>
+  <si>
+    <t>Pit storage</t>
+  </si>
+  <si>
+    <t>Deep litter</t>
+  </si>
+  <si>
+    <t>Poultry manure with bedding</t>
+  </si>
+  <si>
+    <t>Poultry manure without bedding</t>
+  </si>
+  <si>
+    <t>Direct processing</t>
+  </si>
+  <si>
+    <t>Pasture range and paddock</t>
+  </si>
+  <si>
+    <t>MAT raw</t>
   </si>
 </sst>
 </file>
@@ -3231,7 +3288,367 @@
     <cellStyle name="Variable type input" xfId="65" xr:uid="{515940C5-98BF-44F7-AAB8-0D7808DD5C6C}"/>
     <cellStyle name="Variable type other" xfId="66" xr:uid="{5D88A237-9D54-45E0-A48E-F67D0639FDE2}"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="75">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4588,20 +5005,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="59"/>
-      <tableStyleElement type="headerRow" dxfId="58"/>
-      <tableStyleElement type="totalRow" dxfId="57"/>
-      <tableStyleElement type="firstColumn" dxfId="56"/>
-      <tableStyleElement type="firstRowStripe" dxfId="55"/>
-      <tableStyleElement type="secondRowStripe" dxfId="54"/>
+      <tableStyleElement type="wholeTable" dxfId="74"/>
+      <tableStyleElement type="headerRow" dxfId="73"/>
+      <tableStyleElement type="totalRow" dxfId="72"/>
+      <tableStyleElement type="firstColumn" dxfId="71"/>
+      <tableStyleElement type="firstRowStripe" dxfId="70"/>
+      <tableStyleElement type="secondRowStripe" dxfId="69"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="53"/>
-      <tableStyleElement type="headerRow" dxfId="52"/>
-      <tableStyleElement type="totalRow" dxfId="51"/>
-      <tableStyleElement type="firstColumn" dxfId="50"/>
-      <tableStyleElement type="firstRowStripe" dxfId="49"/>
-      <tableStyleElement type="secondRowStripe" dxfId="48"/>
+      <tableStyleElement type="wholeTable" dxfId="68"/>
+      <tableStyleElement type="headerRow" dxfId="67"/>
+      <tableStyleElement type="totalRow" dxfId="66"/>
+      <tableStyleElement type="firstColumn" dxfId="65"/>
+      <tableStyleElement type="firstRowStripe" dxfId="64"/>
+      <tableStyleElement type="secondRowStripe" dxfId="63"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -6342,8 +6759,8 @@
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3287760" cy="182871"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -6602,7 +7019,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -6667,8 +7084,8 @@
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2614114" cy="429926"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -6957,7 +7374,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -8952,8 +9369,8 @@
       <xdr:rowOff>138112</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3236784" cy="429926"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -9284,7 +9701,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -9702,8 +10119,8 @@
       <xdr:rowOff>138112</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2914836" cy="180114"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -9980,7 +10397,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -10444,8 +10861,8 @@
       <xdr:rowOff>147637</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5445080" cy="429926"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -10791,7 +11208,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -10849,6 +11266,26 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10934,34 +11371,34 @@
     <tableColumn id="1" xr3:uid="{3885FE93-299E-44EB-B503-99C305BD6F41}" name="Treatment stage T">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D0E12F95-AC29-47D0-913A-0A0B02931616}" name="MMS m" dataDxfId="47" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D0E12F95-AC29-47D0-913A-0A0B02931616}" name="MMS m" dataDxfId="62" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E17BE7AB-8FAD-4B5C-9F86-E70E6A00B9B1}" name="NSW" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{E17BE7AB-8FAD-4B5C-9F86-E70E6A00B9B1}" name="NSW" dataDxfId="61" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D4C6F922-2719-4479-B7CC-26C5286F73ED}" name="ACT" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{D4C6F922-2719-4479-B7CC-26C5286F73ED}" name="ACT" dataDxfId="60" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5034DCA1-F046-43BC-A94F-832832E6D634}" name="QLD" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{5034DCA1-F046-43BC-A94F-832832E6D634}" name="QLD" dataDxfId="59" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{186521AB-DFC2-4E3B-A674-A5382DCC5ACD}" name="NT" dataDxfId="43" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{186521AB-DFC2-4E3B-A674-A5382DCC5ACD}" name="NT" dataDxfId="58" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{95F9E197-F85F-424A-B68D-774604116729}" name="SA" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{95F9E197-F85F-424A-B68D-774604116729}" name="SA" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{A6DDF652-660B-4C41-982D-FECC3B1142AF}" name="VIC" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{A6DDF652-660B-4C41-982D-FECC3B1142AF}" name="VIC" dataDxfId="56" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5163E1D2-D984-4DBA-95A9-1667F628B2D9}" name="WA" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{5163E1D2-D984-4DBA-95A9-1667F628B2D9}" name="WA" dataDxfId="55" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A0E67108-978C-4849-A310-69F8E4739C6D}" name="TAS" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{A0E67108-978C-4849-A310-69F8E4739C6D}" name="TAS" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{27E929DD-0554-43B8-A58C-34B0A39F2EBA}" name="NIR definition" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{27E929DD-0554-43B8-A58C-34B0A39F2EBA}" name="NIR definition" dataDxfId="53" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10970,20 +11407,20 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C572AF89-905B-44BC-8A3F-912D517AAE52}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{819F82E1-8BFB-49BB-A84C-1541D2694B39}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{789511D5-F916-4716-84A7-B661FF454958}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{70652AFC-F3E8-4421-AFD1-2D686D40D22D}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9B4D5701-070B-47EA-808F-55A6D56454B9}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{1FA7E548-C0EA-432C-8E8B-704642D10B8B}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{36B99C2E-D8A5-44C5-A117-FB42DDC70AF3}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{EBC3E112-1444-44E8-96B3-3CA9BA6303FD}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10992,12 +11429,12 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{25A0C61B-B291-40A8-8D49-74AA36C0A9E2}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4E187021-E65C-4405-B076-51664A260F70}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{372A90AF-1798-43A1-B866-FB6F852E4D72}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{BE8A74F0-502F-4C09-B30D-79967B1CA4B3}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11006,16 +11443,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{BF33ACED-B6E0-4597-87D7-319CDDA4BEEA}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E185DEA7-0F0B-4043-8184-02AAE04CE1D3}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2896061C-8854-433B-968B-8C809664CA9B}" name="Gas">
+    <tableColumn id="1" xr3:uid="{969FB6F5-5748-416A-B0E7-0FA856E9228D}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5A4CA80D-D55E-4246-BBBD-E180168A628B}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{D288383E-5A93-48FA-8608-CEA132940F23}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11024,7 +11461,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{F9C0E0BE-4CA5-4832-98B6-87214FCE264B}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{FC1E3F9B-244C-4BDB-9EAA-280B1B88DFD0}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -11033,19 +11470,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7130C9E7-29A3-4E14-9808-653DC4A6EBFA}" name="Gas">
+    <tableColumn id="1" xr3:uid="{9107412D-787D-4251-B022-2C951856B5CC}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{740B755E-79AB-4F35-9308-D77B9DF1EA5C}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{EDAE218C-BED9-4F30-BC1A-BDA604C52911}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C4E665E-F915-4BFA-B9CC-A0A0F50B22BC}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{7B252330-4D09-4BE1-91E1-8F007E37DA8F}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5DDCAE51-DB13-422D-9FAC-A9C07EC40452}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{EB2A94A6-B09F-44FC-92A1-CCB07CD838C7}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00739614-F51B-406B-AFFB-15BC85E2F83C}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{F2DB3A9E-EA47-4626-8AA6-4142F2BE5B34}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11054,7 +11491,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{2515A5E1-442F-4D54-B329-3693E58A1EAB}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{EC639B46-F2B6-417E-849A-4051D3B16B01}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -11074,52 +11511,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{62AAF798-B15D-4271-927A-A8A3761FCCCC}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{25162FA7-7F7F-4C9C-8231-8FC51C581FD1}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8717C2F5-373F-46C4-9931-0F5D03C661C8}" name="MAT" totalsRowDxfId="19" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{6E2C0A27-43A1-4D92-B3A8-944DC7691E0A}" name="MAT" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C4680CAC-71CD-41BE-8D7D-8DA3A191C6AD}" name="MAP" totalsRowDxfId="18" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{BCEE406F-741C-4AB5-8347-FD3CEB5D1690}" name="MAP" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D4E26F30-4195-4CE8-B4DA-99F110B90518}" name="Frost days per year" totalsRowDxfId="17" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{BF112A88-84E8-4D38-B54C-79713ED69470}" name="Frost days per year" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0DF39DDE-3EFC-4342-A2A9-4182097B7EC1}" name="Elevation" totalsRowDxfId="16" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{DEDF2179-1AFD-46AA-97FF-2C7CC2C8F0A0}" name="Elevation" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3A9CEA3D-76B5-41DC-82F7-4841CE23DEC7}" name="MAP:PET" totalsRowDxfId="15" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{517703E3-C0ED-43E3-909F-4C1979577D3C}" name="MAP:PET" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BC2DED34-2933-4483-B3FF-07D5615064C6}" name="Min temp" totalsRowDxfId="14" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{666A24A7-650A-4B3E-982A-50311730DB7C}" name="Min temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{FF01D565-BF4F-4999-BD32-018FB684F25C}" name="Max temp" totalsRowDxfId="13" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{5604EDD5-66DF-4ECC-BCE6-DD11FD6DB4D6}" name="Max temp" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{7CF1165F-54EC-4690-A7F1-470C0A20CC1D}" name="Min rainfall" totalsRowDxfId="12" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{6DA99F2D-CE18-432C-AB0D-72F425C17C5E}" name="Min rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{AED5C66B-6ACD-48DC-8C8B-05C15217CA0B}" name="Max rainfall" totalsRowDxfId="11" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{BC2916D3-A7D1-4722-A9DC-991CB2F62BD8}" name="Max rainfall" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E41B7A22-BEF4-46C0-8A2D-2792B8AF3565}" name="Min frost days" totalsRowDxfId="10" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{1E64F234-4E02-4B45-A3A1-B18E3FFCFC37}" name="Min frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2027D86C-E675-4004-BA7D-52312C234326}" name="Max frost days" totalsRowDxfId="9" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{70F03B18-1155-4824-8E62-AE5F3FA2A39C}" name="Max frost days" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5CE42D6C-D9F0-43B0-A4CE-78C7DA6F0FF8}" name="Min elevation" totalsRowDxfId="8" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{C3AD9C66-0836-47F7-A64C-E903E6DAF5EE}" name="Min elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{2847C6FC-AAAB-4377-9BB4-0CE7770C5FCD}" name="Max elevation" totalsRowDxfId="7" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{ED33ED06-8D20-47FE-B0B6-650FCDD420E2}" name="Max elevation" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{A1A7A932-493E-40FC-9996-02E450D40A76}" name="Min MAP:PET" totalsRowDxfId="6" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{3C28BB66-16DC-4BC9-BE53-61187001ECC2}" name="Min MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{578E0E27-B0A1-4C90-AC88-4F16A7913682}" name="Max MAP:PET" totalsRowDxfId="5" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{FFF015AD-8516-434B-A94C-11CB9D62F62D}" name="Max MAP:PET" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11128,16 +11565,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B722310D-6971-4BAB-AFE5-8202516612C3}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{B975CFAC-C9D3-4E10-914B-A74776502697}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DE69BEA7-39B3-406C-A179-3B18221DDF1E}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{2BBE1D44-5D3C-421E-B886-5F058BD82B23}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{189B94EF-4D9E-415D-AE6B-6B0CA1291C92}" name="Wet or Dry Zone" totalsRowDxfId="4" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{C3E0B2F3-1F7B-4FCF-B0F4-658087312975}" name="Wet or Dry Zone" totalsRowDxfId="19" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11146,7 +11583,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{267CD803-0212-4268-9BE3-EB85C02DEB9F}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{4F86B9BF-70ED-46B9-A712-EA42AC73454A}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -11154,16 +11591,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6BE43C00-F03D-45FA-9022-CBEC6F19D7A9}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{D5BB3355-DBBC-43C3-9C8D-BC097471993C}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FBCA7201-A92F-4388-958C-42CE0FFD79DD}" name="MAT">
+    <tableColumn id="2" xr3:uid="{15DB6AA7-91D7-4725-9AA9-D1055AF7678C}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B121086D-4424-4F06-A8A1-95295526DD74}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{0AD7766B-F917-4247-BA12-141E5E455D92}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2E75C1A0-DD34-4BCF-A074-7CADBC6AAECF}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{BEC491C5-29B7-47D8-92E3-A6B4AA3DF904}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11172,7 +11609,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{38EA1BB1-D3EC-43B0-AAC0-AD56FD91E835}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{FF94A906-91DA-4FAF-A89B-CEF60B0D1275}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -11180,16 +11617,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DFF1B6AC-5FBD-4901-B46E-31F212F7B6F8}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{3D6E0C09-0BD8-471F-8A53-A12A9E178BF7}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6686DA23-51DE-4D0C-9F66-403D16A247B2}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{13B32985-837D-4685-9D0B-839BCC352710}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0A368BD7-72DA-4958-B1EF-1BD3C7132569}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{81010191-F2A6-4E17-8104-721B45E9D660}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2381BB55-12F0-4B0F-B899-4C2FD4B4AD0F}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{AD6D3163-2840-4E3F-896D-5DF709C34D97}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11198,16 +11635,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{AD529729-CC7C-4857-8578-3AFAF268F778}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{1A2C3C00-7D5E-482F-8CA2-A213D7DF8D38}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4E55CFB5-76E7-423D-96F8-7EF08227B493}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{A4167ABF-B475-4336-9AEE-96008ED98E6B}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{17013B36-DF06-4DE6-977D-1DFEA5424A2D}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{75B56258-627E-484F-9B94-6FD90490B5C5}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11216,16 +11653,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{5DF2B94E-45B2-4CDF-9442-5B40EEB69E87}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{4B10AEB1-ABAB-4497-8F48-0C15CDA46026}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{18980E9C-A83F-4D6E-BF66-3FBC73701726}" name="Data source">
+    <tableColumn id="1" xr3:uid="{48FCAEBE-8FA0-4664-B3AE-973A3E77EF02}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7D04258D-64FF-46A9-AE07-47FEFC4439DF}" name="Data score">
+    <tableColumn id="2" xr3:uid="{F269D724-DA61-40DD-B1DD-62089B53A254}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11241,23 +11678,23 @@
   </autoFilter>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F2B173A3-CADE-4DCA-988D-39EE2392D8DB}" name="MMS"/>
-    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="37" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="52" dataCellStyle="Content normal"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{9B8BF6FA-58E8-4B6F-B021-FC93812D34E0}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{45FE08A5-0001-4080-8F90-757F959BAB2B}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3955BCED-58D4-4A02-A1B0-5CC59B870E09}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{ACC4E2B3-A6FC-4D50-BE90-6D711BFC3B97}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{96C4C42E-00DA-40A3-82DD-B42796163C14}" name="FracWET" dataDxfId="3">
+    <tableColumn id="2" xr3:uid="{35F8284C-32FA-4320-AF32-3F44CCB77CF7}" name="FracWET" dataDxfId="18">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11266,7 +11703,7 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{A5195D22-5B0E-4D62-A1D0-AF1C0E3B177F}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{B985452B-55AC-4EB5-AA25-EAD220463DA8}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -11275,19 +11712,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{DBB0CAC2-4940-4B22-9478-05E62F4BF41D}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{D74A144B-9F75-433D-BE41-D183AF51F2BB}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1B276D85-F6B0-445F-A46F-5CBA8554ACBF}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{87B0476D-5F45-43A5-9823-48327AFBBFC0}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5B1008EA-7DB4-4A48-B7AD-4491BE9D94E9}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{A580C8EE-E9FD-4201-94D1-F99A9BC27373}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{850BD467-00C8-4138-848C-22AC33AF7963}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{50C2C17E-A21C-4FDA-82A8-EF761C0E6BF7}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3819897C-B1C7-4227-911F-F7EF8B9DB32F}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{7F2E249C-6080-446E-8674-6F29CE0873E0}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11296,16 +11733,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{3255CE2F-23D3-4B4F-BF59-D4E33C92CDD1}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{F1D7CB04-0839-425A-B673-CEA7A9C3FB85}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{21644B2F-35C5-46C7-9C1B-01B9C9438466}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{6328C683-420D-4EA6-AF9D-245995DC8FD1}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{44113FA0-3C8F-47F8-BEAF-F6E5E8D642A7}" name="FracWET" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{9E5FEA9D-8FB5-494C-9D24-0E6BFC0C6057}" name="FracWET" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11314,16 +11751,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{F26CA783-9544-4333-9C5C-AC4BB1C7648C}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{E9AFCB04-6C42-4BD7-84F4-CB502355AF0E}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E0DC9C67-4A93-426B-B45D-29C1739DBF9F}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{FB787692-FEAA-422C-9A68-A116E1C1D839}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5B0E4755-347F-4448-8061-D1B2ADD5FCE9}" name="EFPRP" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{AFBB6C89-F456-4C86-80FD-B734DEFDFF30}" name="EFPRP" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11332,16 +11769,16 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{5ABE8FD4-A2A6-4212-89B5-AA9BE5D6132F}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{A23F6973-616E-44B9-9455-AEC834A8AADB}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1B40AF4E-D0D3-47D2-8A92-B9C2CADD3D81}" name="Month">
+    <tableColumn id="1" xr3:uid="{E0DBFFCC-335E-4C29-BC47-5C2A3243CFF0}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{60B3218D-7B8C-4E84-A9EC-F5BEE02E1FC4}" name="Season" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{AC3827EF-FE9E-4E81-A7C7-95A7165D62C5}" name="Season" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11350,6 +11787,80 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{88FD98D7-E5DB-4B28-9E47-A6481BEC1373}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+  <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{8C0CBC0D-B831-4C7E-9F24-0EE0037F3E6B}" name="Temperature zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{B6E0D171-2FBE-46A9-9B1F-1269E55C1B38}" name="MAT (ºC)" dataDxfId="14" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{7FF50BBA-30EE-4E1A-9449-9265A1067683}" name="Anaerobic lagoon" dataDxfId="13" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{53654E61-5BB1-44D1-A97F-E38B4117F28F}" name="Digester / covered lagoons" dataDxfId="12" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{5736C277-B619-4577-BE61-C6F2CFEBBDF4}" name="Liquid systems" dataDxfId="11" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{A4F5FCA7-77C5-40B2-BAC9-EBF849F5559B}" name="Daily spread" dataDxfId="10" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{D7CABD47-531A-49AF-865F-934434068DEC}" name="Composting (passive windrow)" dataDxfId="9" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{5B3C335A-BC58-40E9-8E75-96ED6CCF795D}" name="Solid storage" dataDxfId="8" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{2D3901FD-AFED-45CA-9E32-1204AF6D4874}" name="Pit storage" dataDxfId="7" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{343A0FE7-0AA0-43C9-9A4F-02E9C242020A}" name="Deep litter" dataDxfId="6" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{FAF69A1E-4587-4DCD-9535-2ECADB3A8A73}" name="Poultry manure with bedding" dataDxfId="5" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{9D86AF5D-FDC1-4EE1-9D47-BA4BE96F619F}" name="Poultry manure without bedding" dataDxfId="4" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{C15483D8-6A7E-4D26-B81F-096629F52A98}" name="Direct processing" dataDxfId="3" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{F82A14FE-E6A5-4C72-AE16-87CCAF66B3DB}" name="Direct application" dataDxfId="2" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{DBBFE03E-A035-4E39-B68B-F044C4B1E37F}" name="Pasture range and paddock" dataDxfId="1" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{EE478F66-8602-4161-AB22-52FED9A026F5}" name="MAT raw" dataDxfId="0" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}" name="Table_Data_MMSSymbols" displayName="Table_Data_MMSSymbols" ref="D9:F27" totalsRowShown="0">
   <autoFilter ref="D9:F27" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -11386,22 +11897,22 @@
     <tableColumn id="1" xr3:uid="{FDCB848C-205F-48EA-BACF-F54BCD324E05}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3306F917-B06C-4CC9-B1B1-D97D858E6DAA}" name="Nutrient analysis" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3306F917-B06C-4CC9-B1B1-D97D858E6DAA}" name="Nutrient analysis" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F162F7C2-B0FA-499A-BD58-855C4DF97FA8}" name="Unit" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{F162F7C2-B0FA-499A-BD58-855C4DF97FA8}" name="Unit" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D395A9F5-9A85-4032-A7C1-EC470516DD87}" name="2010-2014" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{D395A9F5-9A85-4032-A7C1-EC470516DD87}" name="2010-2014" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B149E561-7044-4839-B850-C751ABC364C9}" name="2015-2019" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{B149E561-7044-4839-B850-C751ABC364C9}" name="2015-2019" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{ECEB8E53-4880-43AE-9D36-F969D05BCB18}" name="2020-2023" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{ECEB8E53-4880-43AE-9D36-F969D05BCB18}" name="2020-2023" dataDxfId="47" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3B7FAEA4-08D7-48B2-9062-7D93639222CC}" name="2020-2023 Converted to fraction" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{3B7FAEA4-08D7-48B2-9062-7D93639222CC}" name="2020-2023 Converted to fraction" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11424,22 +11935,22 @@
     <tableColumn id="1" xr3:uid="{96F6B4E3-E1EE-445F-9BCE-628B89FC3727}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6B651FD0-BCF6-4081-8A93-6B21A1D6CA99}" name="Characteristic" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6B651FD0-BCF6-4081-8A93-6B21A1D6CA99}" name="Characteristic" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3F266A2B-76EA-4E95-B049-75B8E4AB351F}" name="Unit" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{3F266A2B-76EA-4E95-B049-75B8E4AB351F}" name="Unit" dataDxfId="44" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{15472767-3F72-4A65-88AC-C3242A8E1662}" name="2005-2009" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{15472767-3F72-4A65-88AC-C3242A8E1662}" name="2005-2009" dataDxfId="43" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5F74A8B9-7EFB-4457-8ADA-5E1ABA9DA889}" name="2010-2014" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{5F74A8B9-7EFB-4457-8ADA-5E1ABA9DA889}" name="2010-2014" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E54F2812-2E8B-41EB-98A8-46890B5B4E13}" name="2015-2019" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{E54F2812-2E8B-41EB-98A8-46890B5B4E13}" name="2015-2019" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{88EEE0E3-F5D0-41DF-80EF-59472377C29A}" name="2020-2023" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{88EEE0E3-F5D0-41DF-80EF-59472377C29A}" name="2020-2023" dataDxfId="40" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11457,7 +11968,7 @@
     <tableColumn id="1" xr3:uid="{9D472457-4D8B-44ED-9567-B889D058C2F1}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DurationOfStay_Data(), Table_SourceData_Feedlot_LengthOfStay[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DA3DA009-634B-4C70-926B-C8FB255EB4DC}" name="Length of stay" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DA3DA009-634B-4C70-926B-C8FB255EB4DC}" name="Length of stay" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DurationOfStay_Data(), Table_SourceData_Feedlot_LengthOfStay[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11477,13 +11988,13 @@
     <tableColumn id="1" xr3:uid="{C80C08D8-3F48-4E18-98E3-9B53ACB6C6D9}" name="Treatment stage T">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2BCD8589-5CB8-4ED1-AF2B-2866CEF779A8}" name="MMS m" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2BCD8589-5CB8-4ED1-AF2B-2866CEF779A8}" name="MMS m" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{51E876CD-83B6-49C8-85DD-E2F427A3DCD0}" name="EF mT" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{51E876CD-83B6-49C8-85DD-E2F427A3DCD0}" name="EF mT" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BEDEE6BB-8013-495A-8D74-2C8D37558C98}" name="NIR definition" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{BEDEE6BB-8013-495A-8D74-2C8D37558C98}" name="NIR definition" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11492,7 +12003,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}" name="Table_SourceData_Feedlot_FracGASMmT" displayName="Table_SourceData_Feedlot_FracGASMmT" ref="D112:G117" totalsRowShown="0" headerRowDxfId="20" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}" name="Table_SourceData_Feedlot_FracGASMmT" displayName="Table_SourceData_Feedlot_FracGASMmT" ref="D112:G117" totalsRowShown="0" headerRowDxfId="35" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
   <autoFilter ref="D112:G117" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -11813,26 +12324,34 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB0994D-8D6A-4042-9797-A81886B0D854}">
-  <dimension ref="A1:BX224"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7548F5C8-4326-4B87-AF98-B62783E0FF5C}">
+  <dimension ref="A1:BY250"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="7" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="7" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="48" style="1" customWidth="1"/>
-    <col min="5" max="16" width="20.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="17.28515625" style="1" customWidth="1"/>
-    <col min="18" max="19" width="20.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="4.7109375" style="1" customWidth="1"/>
-    <col min="21" max="32" width="20.7109375" style="7" customWidth="1"/>
-    <col min="33" max="38" width="21.85546875" style="7" customWidth="1"/>
-    <col min="39" max="43" width="20.7109375" style="7" customWidth="1"/>
-    <col min="44" max="64" width="9.140625" style="7"/>
-    <col min="65" max="16384" width="9.140625" style="3"/>
+    <col min="5" max="6" width="20.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="20.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="34.28515625" style="1" customWidth="1"/>
+    <col min="11" max="13" width="20.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="33.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="36.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21" style="1" customWidth="1"/>
+    <col min="17" max="17" width="21.28515625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="31.140625" style="1" customWidth="1"/>
+    <col min="19" max="20" width="20.7109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.7109375" style="1" customWidth="1"/>
+    <col min="22" max="33" width="20.7109375" style="7" customWidth="1"/>
+    <col min="34" max="39" width="21.85546875" style="7" customWidth="1"/>
+    <col min="40" max="44" width="20.7109375" style="7" customWidth="1"/>
+    <col min="45" max="65" width="9.140625" style="7"/>
+    <col min="66" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:65" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -11840,8 +12359,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:64" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -11861,22 +12380,23 @@
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
-      <c r="U3" s="11"/>
+      <c r="U3" s="4"/>
       <c r="V3" s="11"/>
-    </row>
-    <row r="4" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W3" s="11"/>
+    </row>
+    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
-      <c r="BL4" s="3"/>
-    </row>
-    <row r="5" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM4" s="3"/>
+    </row>
+    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="6" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
         <v>Australian states and territories</v>
       </c>
-      <c r="BL5" s="3"/>
-    </row>
-    <row r="6" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM5" s="3"/>
+    </row>
+    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="D6" s="39" t="s">
         <v>21</v>
@@ -11888,7 +12408,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7"/>
       <c r="D7" s="39" t="str" cm="1">
         <f t="array" ref="D7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -11903,7 +12423,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8"/>
       <c r="D8" s="39" t="str" cm="1">
         <f t="array" ref="D8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -11918,7 +12438,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="39" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -11933,7 +12453,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="39" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -11948,7 +12468,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="39" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -11962,9 +12482,9 @@
         <f t="array" ref="F11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>SA</v>
       </c>
-      <c r="BL11" s="3"/>
-    </row>
-    <row r="12" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM11" s="3"/>
+    </row>
+    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="39" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -11978,9 +12498,9 @@
         <f t="array" ref="F12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>WA</v>
       </c>
-      <c r="BL12" s="3"/>
-    </row>
-    <row r="13" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM12" s="3"/>
+    </row>
+    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="39" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -11995,7 +12515,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="39" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -12010,10 +12530,10 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
     <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12582,46 +13102,46 @@
     <row r="78" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="6" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="5" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D83" s="58" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D84" s="58" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D85" s="58" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D86" s="58" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D87" s="58" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="39" t="s">
         <v>10</v>
       </c>
@@ -12670,8 +13190,9 @@
       <c r="S89" s="39" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="90" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T89" s="39"/>
+    </row>
+    <row r="90" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D90" s="39" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical montane</v>
@@ -12736,8 +13257,9 @@
         <f t="array" ref="S90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="91" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T90" s="39"/>
+    </row>
+    <row r="91" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="39" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical wet</v>
@@ -12802,8 +13324,9 @@
         <f t="array" ref="S91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="92" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T91" s="39"/>
+    </row>
+    <row r="92" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D92" s="39" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical moist</v>
@@ -12868,8 +13391,9 @@
         <f t="array" ref="S92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="93" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T92" s="39"/>
+    </row>
+    <row r="93" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D93" s="39" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical dry</v>
@@ -12934,8 +13458,9 @@
         <f t="array" ref="S93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="94" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T93" s="39"/>
+    </row>
+    <row r="94" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D94" s="39" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist</v>
@@ -13000,8 +13525,9 @@
         <f t="array" ref="S94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="95" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T94" s="39"/>
+    </row>
+    <row r="95" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D95" s="39" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry</v>
@@ -13066,8 +13592,9 @@
         <f t="array" ref="S95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T95" s="39"/>
+    </row>
+    <row r="96" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D96" s="39" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate moist</v>
@@ -13132,8 +13659,9 @@
         <f t="array" ref="S96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-    </row>
-    <row r="97" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T96" s="39"/>
+    </row>
+    <row r="97" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D97" s="39" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate dry</v>
@@ -13198,53 +13726,54 @@
         <f t="array" ref="S97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T97" s="39"/>
+    </row>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D98" s="57" t="str" cm="1">
         <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="99" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D99" s="57" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="100" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="57" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="101" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="57" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D102" s="57"/>
     </row>
-    <row r="103" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="6" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D106" s="5" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D107" s="58" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D109" s="39" t="s">
         <v>55</v>
       </c>
@@ -13258,7 +13787,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="110" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D110" s="39" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Warm</v>
@@ -13276,7 +13805,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D111" s="39" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Temperate</v>
@@ -13294,7 +13823,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D112" s="39" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Cool</v>
@@ -13312,33 +13841,33 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D115" s="6" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
         <v>VEERG Australian rainfall zones</v>
       </c>
-      <c r="BM115" s="7"/>
-    </row>
-    <row r="116" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN115" s="7"/>
+    </row>
+    <row r="116" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D116" s="5" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
-      <c r="BM116" s="7"/>
-    </row>
-    <row r="117" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN116" s="7"/>
+    </row>
+    <row r="117" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D117" s="58" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.</v>
       </c>
-      <c r="BM117" s="7"/>
-    </row>
-    <row r="118" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM118" s="7"/>
-    </row>
-    <row r="119" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN117" s="7"/>
+    </row>
+    <row r="118" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN118" s="7"/>
+    </row>
+    <row r="119" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D119" s="39" t="s">
         <v>58</v>
       </c>
@@ -13351,9 +13880,9 @@
       <c r="G119" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="BM119" s="7"/>
-    </row>
-    <row r="120" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN119" s="7"/>
+    </row>
+    <row r="120" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D120" s="39" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>High rainfall</v>
@@ -13370,9 +13899,9 @@
         <f t="array" ref="G120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>999999</v>
       </c>
-      <c r="BM120" s="7"/>
-    </row>
-    <row r="121" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN120" s="7"/>
+    </row>
+    <row r="121" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D121" s="39" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>Low rainfall</v>
@@ -13389,26 +13918,26 @@
         <f t="array" ref="G121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>600</v>
       </c>
-      <c r="BM121" s="7"/>
-    </row>
-    <row r="122" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM122" s="7"/>
-    </row>
-    <row r="123" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN121" s="7"/>
+    </row>
+    <row r="122" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN122" s="7"/>
+    </row>
+    <row r="123" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D124" s="6" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D125" s="5" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D127" s="39" t="s">
         <v>65</v>
       </c>
@@ -13416,7 +13945,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D128" s="39" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Leaching occurs</v>
@@ -13426,7 +13955,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D129" s="39" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Leaching does not occur</v>
@@ -13436,23 +13965,23 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D132" s="6" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E132" s="24"/>
     </row>
-    <row r="133" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D133" s="5" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E133" s="24"/>
     </row>
-    <row r="134" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D134" t="s">
         <v>93</v>
       </c>
@@ -13460,7 +13989,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="135" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
         <v>Yes - in leaching zone</v>
@@ -13470,7 +13999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
         <v>No - not in leaching zone</v>
@@ -13480,9 +14009,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM138" s="7"/>
+    <row r="137" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN138" s="7"/>
       <c r="BO138" s="7"/>
       <c r="BP138" s="7"/>
@@ -13494,13 +14022,13 @@
       <c r="BV138" s="7"/>
       <c r="BW138" s="7"/>
       <c r="BX138" s="7"/>
-    </row>
-    <row r="139" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BY138" s="7"/>
+    </row>
+    <row r="139" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D139" s="6" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
         <v>FracWET for irrigation types</v>
       </c>
-      <c r="BM139" s="7"/>
       <c r="BN139" s="7"/>
       <c r="BO139" s="7"/>
       <c r="BP139" s="7"/>
@@ -13512,13 +14040,13 @@
       <c r="BV139" s="7"/>
       <c r="BW139" s="7"/>
       <c r="BX139" s="7"/>
-    </row>
-    <row r="140" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BY139" s="7"/>
+    </row>
+    <row r="140" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D140" s="5" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
         <v>VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones</v>
       </c>
-      <c r="BM140" s="7"/>
       <c r="BN140" s="7"/>
       <c r="BO140" s="7"/>
       <c r="BP140" s="7"/>
@@ -13530,24 +14058,25 @@
       <c r="BV140" s="7"/>
       <c r="BW140" s="7"/>
       <c r="BX140" s="7"/>
-    </row>
-    <row r="141" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BY140" s="7"/>
+    </row>
+    <row r="141" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D141" s="58" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'</v>
       </c>
-      <c r="BM141" s="7"/>
-    </row>
-    <row r="142" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN141" s="7"/>
+    </row>
+    <row r="142" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D142" s="39" t="s">
         <v>306</v>
       </c>
       <c r="E142" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="BM142" s="7"/>
-    </row>
-    <row r="143" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN142" s="7"/>
+    </row>
+    <row r="143" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D143" s="39" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Not irrigated</v>
@@ -13556,9 +14085,9 @@
         <f t="array" ref="E143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>0</v>
       </c>
-      <c r="BM143" s="7"/>
-    </row>
-    <row r="144" spans="4:76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN143" s="7"/>
+    </row>
+    <row r="144" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Drip irrigation</v>
@@ -13567,9 +14096,9 @@
         <f t="array" ref="E144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>0</v>
       </c>
-      <c r="BM144" s="7"/>
-    </row>
-    <row r="145" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN144" s="7"/>
+    </row>
+    <row r="145" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Sprinkler irrigation</v>
@@ -13578,9 +14107,9 @@
         <f t="array" ref="E145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BM145" s="7"/>
-    </row>
-    <row r="146" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN145" s="7"/>
+    </row>
+    <row r="146" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Surface irrigation</v>
@@ -13589,9 +14118,9 @@
         <f t="array" ref="E146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BM146" s="7"/>
-    </row>
-    <row r="147" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN146" s="7"/>
+    </row>
+    <row r="147" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Other irrigation</v>
@@ -13600,39 +14129,38 @@
         <f t="array" ref="E147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BM147" s="7"/>
-    </row>
-    <row r="148" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM148" s="7"/>
-    </row>
-    <row r="149" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM149" s="7"/>
-    </row>
-    <row r="150" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN147" s="7"/>
+    </row>
+    <row r="148" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN148" s="7"/>
+    </row>
+    <row r="149" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN149" s="7"/>
+    </row>
+    <row r="150" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D150" s="6" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
         <v>Australian data scores for scope 3</v>
       </c>
-      <c r="BM150" s="7"/>
-    </row>
-    <row r="151" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN150" s="7"/>
+    </row>
+    <row r="151" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D151" s="5" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
         <v>VEERG 2026: XXXXXXXX</v>
       </c>
-      <c r="BM151" s="7"/>
-    </row>
-    <row r="152" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM152" s="7"/>
-    </row>
-    <row r="153" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN151" s="7"/>
+    </row>
+    <row r="152" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN152" s="7"/>
+    </row>
+    <row r="153" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D153" s="39" t="s">
         <v>68</v>
       </c>
       <c r="E153" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="BB153" s="3"/>
       <c r="BC153" s="3"/>
       <c r="BD153" s="3"/>
       <c r="BE153" s="3"/>
@@ -13643,8 +14171,9 @@
       <c r="BJ153" s="3"/>
       <c r="BK153" s="3"/>
       <c r="BL153" s="3"/>
-    </row>
-    <row r="154" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM153" s="3"/>
+    </row>
+    <row r="154" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D154" s="39" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>International scope 3 database</v>
@@ -13653,7 +14182,6 @@
         <f t="array" ref="E154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BB154" s="3"/>
       <c r="BC154" s="3"/>
       <c r="BD154" s="3"/>
       <c r="BE154" s="3"/>
@@ -13664,8 +14192,9 @@
       <c r="BJ154" s="3"/>
       <c r="BK154" s="3"/>
       <c r="BL154" s="3"/>
-    </row>
-    <row r="155" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM154" s="3"/>
+    </row>
+    <row r="155" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D155" s="39" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Australian scope 3 database</v>
@@ -13674,7 +14203,6 @@
         <f t="array" ref="E155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>2</v>
       </c>
-      <c r="BB155" s="3"/>
       <c r="BC155" s="3"/>
       <c r="BD155" s="3"/>
       <c r="BE155" s="3"/>
@@ -13685,8 +14213,9 @@
       <c r="BJ155" s="3"/>
       <c r="BK155" s="3"/>
       <c r="BL155" s="3"/>
-    </row>
-    <row r="156" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BM155" s="3"/>
+    </row>
+    <row r="156" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D156" s="39" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>State or regional scope 3 database</v>
@@ -13696,7 +14225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D157" s="39" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Emissions intensity calculated from approved method</v>
@@ -13706,7 +14235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D158" s="39" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Verified credential matching ISO14067</v>
@@ -13716,30 +14245,30 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="4:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="6" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="24"/>
     </row>
-    <row r="162" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="5" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="24"/>
     </row>
-    <row r="163" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="5" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="24"/>
     </row>
-    <row r="164" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="24" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -13748,44 +14277,44 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM165" s="7"/>
+    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="7"/>
       <c r="BO165" s="7"/>
-    </row>
-    <row r="166" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM166" s="7"/>
+      <c r="BP165" s="7"/>
+    </row>
+    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="7"/>
       <c r="BO166" s="7"/>
-    </row>
-    <row r="167" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP166" s="7"/>
+    </row>
+    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="6" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
       </c>
-      <c r="BM167" s="7"/>
       <c r="BN167" s="7"/>
       <c r="BO167" s="7"/>
-    </row>
-    <row r="168" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP167" s="7"/>
+    </row>
+    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="5" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
-      <c r="BM168" s="7"/>
       <c r="BN168" s="7"/>
       <c r="BO168" s="7"/>
-    </row>
-    <row r="169" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP168" s="7"/>
+    </row>
+    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="5" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
       </c>
-      <c r="BM169" s="7"/>
       <c r="BN169" s="7"/>
       <c r="BO169" s="7"/>
-    </row>
-    <row r="170" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP169" s="7"/>
+    </row>
+    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -13793,39 +14322,39 @@
       <c r="E170" s="1">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="BM170" s="7"/>
       <c r="BN170" s="7"/>
       <c r="BO170" s="7"/>
-    </row>
-    <row r="171" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM171" s="7"/>
+      <c r="BP170" s="7"/>
+    </row>
+    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="7"/>
       <c r="BO171" s="7"/>
-    </row>
-    <row r="172" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM172" s="7"/>
+      <c r="BP171" s="7"/>
+    </row>
+    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="7"/>
       <c r="BO172" s="7"/>
-    </row>
-    <row r="173" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP172" s="7"/>
+    </row>
+    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="6" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
       </c>
-      <c r="BM173" s="7"/>
       <c r="BN173" s="7"/>
       <c r="BO173" s="7"/>
-    </row>
-    <row r="174" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP173" s="7"/>
+    </row>
+    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="5" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
       </c>
-      <c r="BM174" s="7"/>
       <c r="BN174" s="7"/>
       <c r="BO174" s="7"/>
-    </row>
-    <row r="175" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP174" s="7"/>
+    </row>
+    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -13834,71 +14363,71 @@
         <f t="array" ref="E175">Common_SourceData.Common_SourceData_DensityOfMethane_Unit()</f>
         <v>kg/m3</v>
       </c>
-      <c r="BM175" s="7"/>
       <c r="BN175" s="7"/>
       <c r="BO175" s="7"/>
-    </row>
-    <row r="176" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM176" s="7"/>
+      <c r="BP175" s="7"/>
+    </row>
+    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="7"/>
       <c r="BO176" s="7"/>
-    </row>
-    <row r="177" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BM177" s="7"/>
+      <c r="BP176" s="7"/>
+    </row>
+    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="7"/>
       <c r="BO177" s="7"/>
-    </row>
-    <row r="178" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP177" s="7"/>
+    </row>
+    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="6" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
       </c>
-      <c r="BM178" s="7"/>
       <c r="BN178" s="7"/>
       <c r="BO178" s="7"/>
-    </row>
-    <row r="179" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP178" s="7"/>
+    </row>
+    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="5" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
       </c>
-      <c r="BM179" s="7"/>
       <c r="BN179" s="7"/>
       <c r="BO179" s="7"/>
-    </row>
-    <row r="180" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BP179" s="7"/>
+    </row>
+    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="57" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="58" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="58" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="58" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="58" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="58" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="39" t="s">
         <v>274</v>
       </c>
@@ -13915,7 +14444,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="187" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="39" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -13937,7 +14466,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="39" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -13959,7 +14488,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="39" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -13981,7 +14510,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="39" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -14003,7 +14532,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="39" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -14025,7 +14554,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="39" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -14387,10 +14916,1332 @@
         <v>Summer</v>
       </c>
     </row>
+    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D227" s="6" t="str" cm="1">
+        <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
+        <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
+      </c>
+    </row>
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D228" s="5" t="str" cm="1">
+        <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
+        <v>VEERG 2026: Table A.1.8.1</v>
+      </c>
+    </row>
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D229" s="58" t="str" cm="1">
+        <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
+        <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
+      </c>
+    </row>
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D231" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E231" s="39" t="s">
+        <v>344</v>
+      </c>
+      <c r="F231" s="38" t="s">
+        <v>345</v>
+      </c>
+      <c r="G231" s="39" t="s">
+        <v>346</v>
+      </c>
+      <c r="H231" s="39" t="s">
+        <v>347</v>
+      </c>
+      <c r="I231" s="39" t="s">
+        <v>348</v>
+      </c>
+      <c r="J231" s="39" t="s">
+        <v>349</v>
+      </c>
+      <c r="K231" s="39" t="s">
+        <v>350</v>
+      </c>
+      <c r="L231" s="39" t="s">
+        <v>351</v>
+      </c>
+      <c r="M231" s="39" t="s">
+        <v>352</v>
+      </c>
+      <c r="N231" s="39" t="s">
+        <v>353</v>
+      </c>
+      <c r="O231" s="39" t="s">
+        <v>354</v>
+      </c>
+      <c r="P231" s="39" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q231" s="39" t="s">
+        <v>329</v>
+      </c>
+      <c r="R231" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="S231" s="39" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D232" s="39" t="str" cm="1">
+        <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E232" s="39" t="str" cm="1">
+        <f t="array" ref="E232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>≤10</v>
+      </c>
+      <c r="F232" s="39" cm="1">
+        <f t="array" ref="F232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.66</v>
+      </c>
+      <c r="G232" s="39" cm="1">
+        <f t="array" ref="G232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H232" s="39" cm="1">
+        <f t="array" ref="H232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="I232" s="39" cm="1">
+        <f t="array" ref="I232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J232" s="39" cm="1">
+        <f t="array" ref="J232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K232" s="39" cm="1">
+        <f t="array" ref="K232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L232" s="39" cm="1">
+        <f t="array" ref="L232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M232" s="39" cm="1">
+        <f t="array" ref="M232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N232" s="39" cm="1">
+        <f t="array" ref="N232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O232" s="39" cm="1">
+        <f t="array" ref="O232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P232" s="39" cm="1">
+        <f t="array" ref="P232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q232" s="39" cm="1">
+        <f t="array" ref="Q232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R232" s="39" cm="1">
+        <f t="array" ref="R232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S232" s="39" cm="1">
+        <f t="array" ref="S232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D233" s="1" t="str" cm="1">
+        <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E233" s="39" cm="1">
+        <f t="array" ref="E233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>11</v>
+      </c>
+      <c r="F233" s="39" cm="1">
+        <f t="array" ref="F233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.68</v>
+      </c>
+      <c r="G233" s="39" cm="1">
+        <f t="array" ref="G233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H233" s="39" cm="1">
+        <f t="array" ref="H233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.11</v>
+      </c>
+      <c r="I233" s="39" cm="1">
+        <f t="array" ref="I233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J233" s="39" cm="1">
+        <f t="array" ref="J233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K233" s="39" cm="1">
+        <f t="array" ref="K233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L233" s="39" cm="1">
+        <f t="array" ref="L233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M233" s="39" cm="1">
+        <f t="array" ref="M233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N233" s="39" cm="1">
+        <f t="array" ref="N233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O233" s="39" cm="1">
+        <f t="array" ref="O233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P233" s="39" cm="1">
+        <f t="array" ref="P233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q233" s="39" cm="1">
+        <f t="array" ref="Q233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R233" s="39" cm="1">
+        <f t="array" ref="R233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S233" s="39" cm="1">
+        <f t="array" ref="S233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D234" s="1" t="str" cm="1">
+        <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E234" s="39" cm="1">
+        <f t="array" ref="E234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>12</v>
+      </c>
+      <c r="F234" s="39" cm="1">
+        <f t="array" ref="F234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.7</v>
+      </c>
+      <c r="G234" s="39" cm="1">
+        <f t="array" ref="G234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H234" s="39" cm="1">
+        <f t="array" ref="H234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.13</v>
+      </c>
+      <c r="I234" s="39" cm="1">
+        <f t="array" ref="I234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J234" s="39" cm="1">
+        <f t="array" ref="J234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K234" s="39" cm="1">
+        <f t="array" ref="K234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L234" s="39" cm="1">
+        <f t="array" ref="L234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M234" s="39" cm="1">
+        <f t="array" ref="M234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N234" s="39" cm="1">
+        <f t="array" ref="N234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O234" s="39" cm="1">
+        <f t="array" ref="O234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P234" s="39" cm="1">
+        <f t="array" ref="P234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q234" s="39" cm="1">
+        <f t="array" ref="Q234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R234" s="39" cm="1">
+        <f t="array" ref="R234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S234" s="39" cm="1">
+        <f t="array" ref="S234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D235" s="1" t="str" cm="1">
+        <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E235" s="39" cm="1">
+        <f t="array" ref="E235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>13</v>
+      </c>
+      <c r="F235" s="39" cm="1">
+        <f t="array" ref="F235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.71</v>
+      </c>
+      <c r="G235" s="39" cm="1">
+        <f t="array" ref="G235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H235" s="39" cm="1">
+        <f t="array" ref="H235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I235" s="39" cm="1">
+        <f t="array" ref="I235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J235" s="39" cm="1">
+        <f t="array" ref="J235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K235" s="39" cm="1">
+        <f t="array" ref="K235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L235" s="39" cm="1">
+        <f t="array" ref="L235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M235" s="39" cm="1">
+        <f t="array" ref="M235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N235" s="39" cm="1">
+        <f t="array" ref="N235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O235" s="39" cm="1">
+        <f t="array" ref="O235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P235" s="39" cm="1">
+        <f t="array" ref="P235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q235" s="39" cm="1">
+        <f t="array" ref="Q235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R235" s="39" cm="1">
+        <f t="array" ref="R235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S235" s="39" cm="1">
+        <f t="array" ref="S235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D236" s="1" t="str" cm="1">
+        <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E236" s="39" cm="1">
+        <f t="array" ref="E236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>14</v>
+      </c>
+      <c r="F236" s="39" cm="1">
+        <f t="array" ref="F236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.73</v>
+      </c>
+      <c r="G236" s="39" cm="1">
+        <f t="array" ref="G236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H236" s="39" cm="1">
+        <f t="array" ref="H236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.15</v>
+      </c>
+      <c r="I236" s="39" cm="1">
+        <f t="array" ref="I236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J236" s="39" cm="1">
+        <f t="array" ref="J236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K236" s="39" cm="1">
+        <f t="array" ref="K236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L236" s="39" cm="1">
+        <f t="array" ref="L236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M236" s="39" cm="1">
+        <f t="array" ref="M236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N236" s="39" cm="1">
+        <f t="array" ref="N236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O236" s="39" cm="1">
+        <f t="array" ref="O236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P236" s="39" cm="1">
+        <f t="array" ref="P236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q236" s="39" cm="1">
+        <f t="array" ref="Q236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R236" s="39" cm="1">
+        <f t="array" ref="R236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S236" s="39" cm="1">
+        <f t="array" ref="S236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D237" s="1" t="str" cm="1">
+        <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E237" s="39" cm="1">
+        <f t="array" ref="E237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>15</v>
+      </c>
+      <c r="F237" s="39" cm="1">
+        <f t="array" ref="F237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.74</v>
+      </c>
+      <c r="G237" s="39" cm="1">
+        <f t="array" ref="G237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H237" s="39" cm="1">
+        <f t="array" ref="H237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.17</v>
+      </c>
+      <c r="I237" s="39" cm="1">
+        <f t="array" ref="I237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J237" s="39" cm="1">
+        <f t="array" ref="J237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K237" s="39" cm="1">
+        <f t="array" ref="K237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L237" s="39" cm="1">
+        <f t="array" ref="L237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M237" s="39" cm="1">
+        <f t="array" ref="M237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N237" s="39" cm="1">
+        <f t="array" ref="N237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O237" s="39" cm="1">
+        <f t="array" ref="O237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P237" s="39" cm="1">
+        <f t="array" ref="P237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q237" s="39" cm="1">
+        <f t="array" ref="Q237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R237" s="39" cm="1">
+        <f t="array" ref="R237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S237" s="39" cm="1">
+        <f t="array" ref="S237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D238" s="1" t="str" cm="1">
+        <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E238" s="39" cm="1">
+        <f t="array" ref="E238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>16</v>
+      </c>
+      <c r="F238" s="39" cm="1">
+        <f t="array" ref="F238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.75</v>
+      </c>
+      <c r="G238" s="39" cm="1">
+        <f t="array" ref="G238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H238" s="39" cm="1">
+        <f t="array" ref="H238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="I238" s="39" cm="1">
+        <f t="array" ref="I238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J238" s="39" cm="1">
+        <f t="array" ref="J238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K238" s="39" cm="1">
+        <f t="array" ref="K238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L238" s="39" cm="1">
+        <f t="array" ref="L238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M238" s="39" cm="1">
+        <f t="array" ref="M238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N238" s="39" cm="1">
+        <f t="array" ref="N238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O238" s="39" cm="1">
+        <f t="array" ref="O238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P238" s="39" cm="1">
+        <f t="array" ref="P238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q238" s="39" cm="1">
+        <f t="array" ref="Q238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R238" s="39" cm="1">
+        <f t="array" ref="R238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S238" s="39" cm="1">
+        <f t="array" ref="S238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D239" s="1" t="str" cm="1">
+        <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E239" s="39" cm="1">
+        <f t="array" ref="E239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>17</v>
+      </c>
+      <c r="F239" s="39" cm="1">
+        <f t="array" ref="F239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.76</v>
+      </c>
+      <c r="G239" s="39" cm="1">
+        <f t="array" ref="G239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H239" s="39" cm="1">
+        <f t="array" ref="H239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.2</v>
+      </c>
+      <c r="I239" s="39" cm="1">
+        <f t="array" ref="I239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J239" s="39" cm="1">
+        <f t="array" ref="J239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K239" s="39" cm="1">
+        <f t="array" ref="K239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L239" s="39" cm="1">
+        <f t="array" ref="L239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M239" s="39" cm="1">
+        <f t="array" ref="M239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N239" s="39" cm="1">
+        <f t="array" ref="N239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O239" s="39" cm="1">
+        <f t="array" ref="O239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P239" s="39" cm="1">
+        <f t="array" ref="P239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q239" s="39" cm="1">
+        <f t="array" ref="Q239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R239" s="39" cm="1">
+        <f t="array" ref="R239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S239" s="39" cm="1">
+        <f t="array" ref="S239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D240" s="1" t="str" cm="1">
+        <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E240" s="39" cm="1">
+        <f t="array" ref="E240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>18</v>
+      </c>
+      <c r="F240" s="39" cm="1">
+        <f t="array" ref="F240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.77</v>
+      </c>
+      <c r="G240" s="39" cm="1">
+        <f t="array" ref="G240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H240" s="39" cm="1">
+        <f t="array" ref="H240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.22</v>
+      </c>
+      <c r="I240" s="39" cm="1">
+        <f t="array" ref="I240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J240" s="39" cm="1">
+        <f t="array" ref="J240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K240" s="39" cm="1">
+        <f t="array" ref="K240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L240" s="39" cm="1">
+        <f t="array" ref="L240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M240" s="39" cm="1">
+        <f t="array" ref="M240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N240" s="39" cm="1">
+        <f t="array" ref="N240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O240" s="39" cm="1">
+        <f t="array" ref="O240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P240" s="39" cm="1">
+        <f t="array" ref="P240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q240" s="39" cm="1">
+        <f t="array" ref="Q240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R240" s="39" cm="1">
+        <f t="array" ref="R240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S240" s="39" cm="1">
+        <f t="array" ref="S240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D241" s="1" t="str" cm="1">
+        <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E241" s="39" cm="1">
+        <f t="array" ref="E241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>19</v>
+      </c>
+      <c r="F241" s="39" cm="1">
+        <f t="array" ref="F241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.77</v>
+      </c>
+      <c r="G241" s="39" cm="1">
+        <f t="array" ref="G241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H241" s="39" cm="1">
+        <f t="array" ref="H241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.24</v>
+      </c>
+      <c r="I241" s="39" cm="1">
+        <f t="array" ref="I241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J241" s="39" cm="1">
+        <f t="array" ref="J241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K241" s="39" cm="1">
+        <f t="array" ref="K241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L241" s="39" cm="1">
+        <f t="array" ref="L241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M241" s="39" cm="1">
+        <f t="array" ref="M241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N241" s="39" cm="1">
+        <f t="array" ref="N241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O241" s="39" cm="1">
+        <f t="array" ref="O241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P241" s="39" cm="1">
+        <f t="array" ref="P241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q241" s="39" cm="1">
+        <f t="array" ref="Q241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R241" s="39" cm="1">
+        <f t="array" ref="R241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S241" s="39" cm="1">
+        <f t="array" ref="S241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D242" s="1" t="str" cm="1">
+        <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E242" s="39" cm="1">
+        <f t="array" ref="E242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>20</v>
+      </c>
+      <c r="F242" s="39" cm="1">
+        <f t="array" ref="F242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.78</v>
+      </c>
+      <c r="G242" s="39" cm="1">
+        <f t="array" ref="G242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H242" s="39" cm="1">
+        <f t="array" ref="H242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.26</v>
+      </c>
+      <c r="I242" s="39" cm="1">
+        <f t="array" ref="I242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J242" s="39" cm="1">
+        <f t="array" ref="J242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K242" s="39" cm="1">
+        <f t="array" ref="K242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L242" s="39" cm="1">
+        <f t="array" ref="L242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M242" s="39" cm="1">
+        <f t="array" ref="M242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N242" s="39" cm="1">
+        <f t="array" ref="N242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O242" s="39" cm="1">
+        <f t="array" ref="O242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P242" s="39" cm="1">
+        <f t="array" ref="P242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q242" s="39" cm="1">
+        <f t="array" ref="Q242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R242" s="39" cm="1">
+        <f t="array" ref="R242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S242" s="39" cm="1">
+        <f t="array" ref="S242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D243" s="1" t="str" cm="1">
+        <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E243" s="39" cm="1">
+        <f t="array" ref="E243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>21</v>
+      </c>
+      <c r="F243" s="39" cm="1">
+        <f t="array" ref="F243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.78</v>
+      </c>
+      <c r="G243" s="39" cm="1">
+        <f t="array" ref="G243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H243" s="39" cm="1">
+        <f t="array" ref="H243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I243" s="39" cm="1">
+        <f t="array" ref="I243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J243" s="39" cm="1">
+        <f t="array" ref="J243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K243" s="39" cm="1">
+        <f t="array" ref="K243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L243" s="39" cm="1">
+        <f t="array" ref="L243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M243" s="39" cm="1">
+        <f t="array" ref="M243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N243" s="39" cm="1">
+        <f t="array" ref="N243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O243" s="39" cm="1">
+        <f t="array" ref="O243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P243" s="39" cm="1">
+        <f t="array" ref="P243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q243" s="39" cm="1">
+        <f t="array" ref="Q243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R243" s="39" cm="1">
+        <f t="array" ref="R243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S243" s="39" cm="1">
+        <f t="array" ref="S243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D244" s="1" t="str" cm="1">
+        <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E244" s="39" cm="1">
+        <f t="array" ref="E244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>22</v>
+      </c>
+      <c r="F244" s="39" cm="1">
+        <f t="array" ref="F244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.78</v>
+      </c>
+      <c r="G244" s="39" cm="1">
+        <f t="array" ref="G244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H244" s="39" cm="1">
+        <f t="array" ref="H244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.31</v>
+      </c>
+      <c r="I244" s="39" cm="1">
+        <f t="array" ref="I244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J244" s="39" cm="1">
+        <f t="array" ref="J244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K244" s="39" cm="1">
+        <f t="array" ref="K244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L244" s="39" cm="1">
+        <f t="array" ref="L244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M244" s="39" cm="1">
+        <f t="array" ref="M244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N244" s="39" cm="1">
+        <f t="array" ref="N244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O244" s="39" cm="1">
+        <f t="array" ref="O244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P244" s="39" cm="1">
+        <f t="array" ref="P244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q244" s="39" cm="1">
+        <f t="array" ref="Q244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R244" s="39" cm="1">
+        <f t="array" ref="R244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S244" s="39" cm="1">
+        <f t="array" ref="S244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D245" s="1" t="str" cm="1">
+        <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E245" s="39" cm="1">
+        <f t="array" ref="E245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>23</v>
+      </c>
+      <c r="F245" s="39" cm="1">
+        <f t="array" ref="F245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G245" s="39" cm="1">
+        <f t="array" ref="G245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H245" s="39" cm="1">
+        <f t="array" ref="H245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.34</v>
+      </c>
+      <c r="I245" s="39" cm="1">
+        <f t="array" ref="I245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J245" s="39" cm="1">
+        <f t="array" ref="J245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K245" s="39" cm="1">
+        <f t="array" ref="K245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L245" s="39" cm="1">
+        <f t="array" ref="L245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M245" s="39" cm="1">
+        <f t="array" ref="M245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N245" s="39" cm="1">
+        <f t="array" ref="N245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O245" s="39" cm="1">
+        <f t="array" ref="O245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P245" s="39" cm="1">
+        <f t="array" ref="P245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q245" s="39" cm="1">
+        <f t="array" ref="Q245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R245" s="39" cm="1">
+        <f t="array" ref="R245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S245" s="39" cm="1">
+        <f t="array" ref="S245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D246" s="1" t="str" cm="1">
+        <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E246" s="39" cm="1">
+        <f t="array" ref="E246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>24</v>
+      </c>
+      <c r="F246" s="39" cm="1">
+        <f t="array" ref="F246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G246" s="39" cm="1">
+        <f t="array" ref="G246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H246" s="39" cm="1">
+        <f t="array" ref="H246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.37</v>
+      </c>
+      <c r="I246" s="39" cm="1">
+        <f t="array" ref="I246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J246" s="39" cm="1">
+        <f t="array" ref="J246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K246" s="39" cm="1">
+        <f t="array" ref="K246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L246" s="39" cm="1">
+        <f t="array" ref="L246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M246" s="39" cm="1">
+        <f t="array" ref="M246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N246" s="39" cm="1">
+        <f t="array" ref="N246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O246" s="39" cm="1">
+        <f t="array" ref="O246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P246" s="39" cm="1">
+        <f t="array" ref="P246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q246" s="39" cm="1">
+        <f t="array" ref="Q246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R246" s="39" cm="1">
+        <f t="array" ref="R246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S246" s="39" cm="1">
+        <f t="array" ref="S246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D247" s="1" t="str" cm="1">
+        <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E247" s="39" cm="1">
+        <f t="array" ref="E247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>25</v>
+      </c>
+      <c r="F247" s="39" cm="1">
+        <f t="array" ref="F247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G247" s="39" cm="1">
+        <f t="array" ref="G247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H247" s="39" cm="1">
+        <f t="array" ref="H247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.41</v>
+      </c>
+      <c r="I247" s="39" cm="1">
+        <f t="array" ref="I247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J247" s="39" cm="1">
+        <f t="array" ref="J247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K247" s="39" cm="1">
+        <f t="array" ref="K247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L247" s="39" cm="1">
+        <f t="array" ref="L247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M247" s="39" cm="1">
+        <f t="array" ref="M247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N247" s="39" cm="1">
+        <f t="array" ref="N247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O247" s="39" cm="1">
+        <f t="array" ref="O247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P247" s="39" cm="1">
+        <f t="array" ref="P247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q247" s="39" cm="1">
+        <f t="array" ref="Q247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R247" s="39" cm="1">
+        <f t="array" ref="R247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S247" s="39" cm="1">
+        <f t="array" ref="S247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D248" s="1" t="str" cm="1">
+        <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Warm</v>
+      </c>
+      <c r="E248" s="39" cm="1">
+        <f t="array" ref="E248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>26</v>
+      </c>
+      <c r="F248" s="39" cm="1">
+        <f t="array" ref="F248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G248" s="39" cm="1">
+        <f t="array" ref="G248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H248" s="39" cm="1">
+        <f t="array" ref="H248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.44</v>
+      </c>
+      <c r="I248" s="39" cm="1">
+        <f t="array" ref="I248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="J248" s="39" cm="1">
+        <f t="array" ref="J248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K248" s="39" cm="1">
+        <f t="array" ref="K248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L248" s="39" cm="1">
+        <f t="array" ref="L248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M248" s="39" cm="1">
+        <f t="array" ref="M248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N248" s="39" cm="1">
+        <f t="array" ref="N248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O248" s="39" cm="1">
+        <f t="array" ref="O248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P248" s="39" cm="1">
+        <f t="array" ref="P248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q248" s="39" cm="1">
+        <f t="array" ref="Q248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R248" s="39" cm="1">
+        <f t="array" ref="R248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S248" s="39" cm="1">
+        <f t="array" ref="S248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D249" s="1" t="str" cm="1">
+        <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Warm</v>
+      </c>
+      <c r="E249" s="39" cm="1">
+        <f t="array" ref="E249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>27</v>
+      </c>
+      <c r="F249" s="39" cm="1">
+        <f t="array" ref="F249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G249" s="39" cm="1">
+        <f t="array" ref="G249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H249" s="39" cm="1">
+        <f t="array" ref="H249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.48</v>
+      </c>
+      <c r="I249" s="39" cm="1">
+        <f t="array" ref="I249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="J249" s="39" cm="1">
+        <f t="array" ref="J249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K249" s="39" cm="1">
+        <f t="array" ref="K249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L249" s="39" cm="1">
+        <f t="array" ref="L249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M249" s="39" cm="1">
+        <f t="array" ref="M249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N249" s="39" cm="1">
+        <f t="array" ref="N249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O249" s="39" cm="1">
+        <f t="array" ref="O249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P249" s="39" cm="1">
+        <f t="array" ref="P249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q249" s="39" cm="1">
+        <f t="array" ref="Q249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R249" s="39" cm="1">
+        <f t="array" ref="R249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S249" s="39" cm="1">
+        <f t="array" ref="S249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D250" s="1" t="str" cm="1">
+        <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Warm</v>
+      </c>
+      <c r="E250" s="39" t="str" cm="1">
+        <f t="array" ref="E250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>≥28</v>
+      </c>
+      <c r="F250" s="39" cm="1">
+        <f t="array" ref="F250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G250" s="39" cm="1">
+        <f t="array" ref="G250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H250" s="39" cm="1">
+        <f t="array" ref="H250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.5</v>
+      </c>
+      <c r="I250" s="39" cm="1">
+        <f t="array" ref="I250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="J250" s="39" cm="1">
+        <f t="array" ref="J250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K250" s="39" cm="1">
+        <f t="array" ref="K250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L250" s="39" cm="1">
+        <f t="array" ref="L250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M250" s="39" cm="1">
+        <f t="array" ref="M250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N250" s="39" cm="1">
+        <f t="array" ref="N250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O250" s="39" cm="1">
+        <f t="array" ref="O250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P250" s="39" cm="1">
+        <f t="array" ref="P250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q250" s="39" cm="1">
+        <f t="array" ref="Q250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R250" s="39" cm="1">
+        <f t="array" ref="R250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S250" s="39" cm="1">
+        <f t="array" ref="S250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="15">
-    <tablePart r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="16">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -14405,6 +16256,8 @@
     <tablePart r:id="rId13"/>
     <tablePart r:id="rId14"/>
     <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId17"/>
   </tableParts>
 </worksheet>
 </file>
@@ -28088,6 +29941,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXABuAEYAcgBhAGMAVwBFAFQATQBNAFMAaQAgAD0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuACgAVABhAGIAbABlACAAQQA1AC4ANQAuADEAMAAuADIAIABpAHMAIAByAGUAZgBlAHIAZQBuAGMAZQBkACAAaQBuACAATgBJAFIAIABiAHUAdAAgADEAIABpAHMAIAB1AHMAZQBkACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4ANQBhAF8AMwAsACAAMwAuAEIALgA1AGMAXwAzACwAIAAzAC4AQgAuADUAZABfADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMQApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAFwAbgBGAHIAYQBjAEwARQBBAEMASABfAE0AUwAgAD0AIAAwAC4AMAAyACAAKABHAGcAIABOAC8ARwBnACAAYQBwAHAAbABpAGUAZAApACAAKABDAFMAIABFAEYALAAgAHMAbwB1AHIAYwBlACAASQBQAEMAQwAgACgAMgAwADEAOQApACkAIABcAG4AZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4ANQBhAF8AMwAsACAAMwAuAEIALgA1AGMAXwAzACwAIAAzAC4AQgAuADUAZABfADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA1ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAIAAwAC4AMAAwADQAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAYwBhAG4AZQBcACIALAAgADAALgAwADEAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgADAALgAwADAANQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAZQBcACIALAAgADAALgAwADAANgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAFwAbgBUAGEAYgBsAGUAIAA1AC4AMQAyACAAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAHMAeQBtAGIAbwBsAHMAIAB1AHMAZQBkACAAaQBuACAAYQBsAGcAbwByAGkAdABoAG0AcwAgAGYAbwByACAAbQBhAG4AdQByAGUAIAByAGUAbABhAHQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIAA1AC4AMQAyACAAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAHMAeQBtAGIAbwBsAHMAIAB1AHMAZQBkACAAaQBuACAAYQBsAGcAbwByAGkAdABoAG0AcwAgAGYAbwByACAAbQBhAG4AdQByAGUAIAByAGUAbABhAHQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAFQAYQBiAGwAZQAgADUALgAxADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAeQBtAGIAbwBsAFwAIgAsACAAXAAiAE0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAG0APQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAyAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAIAAoAG0APQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABtAD0AMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMwBhAFwAIgAsACAAXAAiAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQAgACgAbQA9ADMAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMwBiAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAzAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADQAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAKABtAD0ANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApACAAKABtAD0ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANgBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAIAAoAG0APQA2ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA3AFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAIAAoAG0APQA3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA4AFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAIAAoAG0APQA4ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA5AFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA5ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADAAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAIAAoAG0APQAxADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMQBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGEAXAAiACwAIABcACIAQgBlAGwAdAAgAG0AYQBuAHUAcgBlACAAcgBlAG0AbwB2AGEAbABcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsACAAKABtAD0AMQAxAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMQBiAFwAIgAsACAAXAAiAE0AYQBuAHUAcgBlACAAcwB0AG8AcgBlAGQAIABpAG4AIABoAG8AdQBzAGUAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQAgACgAbQA9ADEAMQBiACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgACgAbQA9ADEAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAzAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABtAD0AMQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADQAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrACAAKABtAD0AMQA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0ACIALAAiAHQAZQB4AHQAIgA6ACIALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAEwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANQApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdABvACAAZQBhAGMAaAAgAHQAZQByAHQAaQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAYQBzAHMAdQBtAGUAZAAgAHQAaABhAHQAIAAyACAAcABlAHIAIABjAGUAbgB0ACAAaQBzACAAcgB1AG4AIAAtACAAbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABmAGUAZQBkACAAcABhAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdABvACAAZQBhAGMAaAAgAHQAZQByAHQAaQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAYQBzAHMAdQBtAGUAZAAgAHQAaABhAHQAIAAyACAAcABlAHIAIABjAGUAbgB0ACAAaQBzACAAcgB1AG4AIAAtACAAbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABmAGUAZQBkACAAcABhAGQALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBtADEAVAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAyACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADEANgApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADEAOQApADsAXABuAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMQBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAyAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIABNAE0AUwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADMATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAeABwAG8AcgB0ACAAbQBpAGQAIABmAGUAZABcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHgAcABvAHIAdAAgAGwAbwBuAGcAIABmAGUAZABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAxADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBlAGQAbABvAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAEwAZQBuAGcAdABoACAAbwBmACAAUwB0AGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiADEALQA4ADAAIABkAGEAeQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiADgAMQAtADIAMAAwACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiADIAMAAxACsAIABkAGEAeQBzAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAyADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbwB2AGUAZAAgAGYAZQBlAGQAbABvAHQAIAB0AHkAcABlAHMAIAB0AG8AIABhACAAcwBlAHAAYQByAGEAdABlACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AYQBtAGUAZAAgAFwAdQAwADAAMgA3AGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAALQAgAG8AcgBpAGcAaQBuAGEAbAAgAGgAYQBzACAAaABlAGEAZABlAHIAIABcAHUAMAAwADIANwBVAG4AaQB0AFwAdQAwADAAMgA3ACAAdwBoAGkAYwBoACAAYwBvAHYAZQByAHMAIAB0AHcAbwAgAGMAbwBsAHUAbQBuAHMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA3ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAA3ADAALAAgADcAMAAsACAANwAwACwAIAA3ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBkAGEAeQBcACIALAAgADEAMAAuADAALAAgADEAMAAuADAALAAgADEAMAAuADQALAAgADEAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADIAMQAuADEALAAgADIAMAAuADQALAAgADIAMAAuADQALAAgADIAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAMQAxADUALAAgADEAMQA1ACwAIAAxADIAMAAsACAAMQA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADEALgAyACwAIAAxADAALgA4ACwAIAAxADAALgA4ACwAIAAxADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAAMQAyAC4ANQAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADIANQAwACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAA5AC4AMAAsACAAOAAuADUALAAgADgALgAyACwAIAA4AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAANgAuADYALAAgADcALgAwACwAIAA3AC4AMAAsACAANwAuADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABcAHUAMAAwADIANwBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgAgAGMAbwBsAHUAbQBuACAAYQBuAGQAIABjAG8AbgB2AGUAcgB0AGUAZAAgAE4ARABGACAAYQBuAGQAIABFAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAdgBhAGwAdQBlAHMAIAB0AG8AIABmAHIAYQBjAHQAaQBvAG4AcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAA4ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBOAHUAdAByAGkAZQBuAHQAIABhAG4AYQBsAHkAcwBpAHMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgAzAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA0AC4ANQAsACAANAAuADUALAAgADQALgA4ACwAIAA0AC4AOAAsACAAMAAuADAANAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgA0AC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADAALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAwAC4AMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADUALAAgADUALgA1ACwAIAAwAC4AMAA1ADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA0ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE0AQwBGAHMAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAATQBDAEYAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAE4AUwBXACAAdgBhAGwAdQBlAHMAIABmAG8AcgAgAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABOAFQAIABhAG4AZAAgAFQAQQBTACAAYwBvAGwAdQBtAG4AcwAgAHcAaQB0AGgAIABcAHUAMAAwADIANwBuAG8AIABkAGEAdABhAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADEAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIABUAFwAIgAsACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBOAFQAXAAiACwAIABcACIAUwBBAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFcAQQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBpAG0AYQByAHkAXAAiACwAIABcACIARAByAHkAIABsAG8AdAAgACgARgBlAGUAZABwAGEAZAApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMwAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgADAALAAgADAALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA3ACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIAAoAEUARgBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFQAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBpAG0AYQByAHkAXAAiACwAIABcACIARAByAHkAIABsAG8AdAAgACgARgBlAGUAZABwAGEAZAApAFwAIgAsACAAMAAuADAAMAA1ADQALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAUABvAG4AZAApAFwAIgAsACAAMAAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIABUAFwAIgAsACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQBUACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4ANgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAyADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADQALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAKQBcACIALAAgADAALgAzADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAE0AZQB0AGgAYQBuAGUAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBFAF8AQwBIADQAXABuAHQAIABDAEgANABcAG4AewBFAH0AXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAEQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAATgBfAHsAagB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAbgBEAF8AagAgAD0AIABsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAZABhAHkAcwBcAG4ATQBfAGoAbQBUACAAPQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcABlAHIAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAsACAATQBNAFMALAAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAA6ACAAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByAHMAIABvAGYAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGgAZQBhAGQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQAXwBqACwAIABNAF8AagBtAFQALAAgAE4AXwBqACwAXABuACAAIAAgACAAKABEAF8AagAgACoAIABNAF8AagBtAFQAIAAqACAATgBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB7AEUAfQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgARABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALABcACIAbABlAG4AZwB0AGgAIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAG0AVABcACIALABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGoAXAAiACwAXAAiAG4AdQBtAGIAZQByAHMAIABvAGYAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGgAZQBhAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcAG4ATQBfAGoAbQA1AFQAMQBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAXwBqACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBfAG0ANQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAXwBpAG0ANQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAF8AagAsACAAQgBPACwAIABNAE0AUwBfAG0ANQBUADEALAAgAE0AQwBGAF8AaQBtADUALAAgAHIAaABvACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAATQBDAEYAXwBpAG0ANQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgATQBDAEYAXwBpAG0ANQApACwAIABNAEMARgBfAGkAbQA1ACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAVgBTAF8AagAgACoAIABCAE8AIAAqACAATQBNAFMAXwBtADUAVAAxACAAKgAgAE0AQwBGAF8AaQBtADUAIAAqACAAcgBoAG8AXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0ANQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtADUAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQA1AFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBfAGoAbQBUADIAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAG0AVAA9ADIAfQA9ACgAMQAtAFYAUwBMACkAXABcAHQAaQBtAGUAcwAgAFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMATAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAFYAUwBfAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAF8AbQBUADIAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAF8AaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAEwALAAgAFYAUwBfAGoALAAgAEIATwAsACAATQBNAFMAXwBtAFQAMgAsACAATQBDAEYAXwBpAG0ALAAgAHIAaABvACwAXABuACAAIAAgACAAKAAxACAALQAgAFYAUwBMACkAIAAqACAAVgBTAF8AagAgACoAIABCAE8AIAAqACAATQBNAFMAXwBtAFQAMgAgACoAIABNAEMARgBfAGkAbQAgACoAIAByAGgAbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBqAG0AVAA9ADIAfQA9ACgAMQAtAFYAUwBMACkAXABcAHQAaQBtAGUAcwAgAFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBMAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXABuAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXABuAE0AXwBqAG0AMQBUADMAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAG0APQAxACwAVAA9ADMAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAD0AMQAsAFQAPQAzAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0APQAxAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAF8AagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAXwBtADEAVAAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAXwBpAG0AMQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAXwBqACwAIABCAE8ALAAgAE0ATQBTAF8AbQAxAFQAMwAsACAATQBDAEYAXwBpAG0AMQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABWAFMAXwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBfAG0AMQBUADMAIAAqACAATQBDAEYAXwBpAG0AMQAgACoAIAByAGgAbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQA9ADEALABUAD0AMwB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQAxACwAVAA9ADMAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADEAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgAGoAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AbQAxAFQAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIAB0AGUAcgB0AGkAYQByAHkAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQAxAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAFMAXwBqAFwAbgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAFYAUwBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARABNAEQAXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AQQApAFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBEAE0ARABfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBBACAAPQAgAGEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABEAE0ARABfAGoALAAgAEEALABcAG4AIAAgACAAIABJAF8AagAgACoAIAAoADEAIAAtACAARABNAEQAXwBqACkAIAAqACAAKAAxACAALQAgAEEAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAXwB7AGoAfQA9AEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAEQATQBEAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzACgAMQAtAEEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAZgBvAHIAIABlAGEAYwBoACAAZwByAG8AdQBwACAAagAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBEAF8AagBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIABqACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBcACIALABcACIAYQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQA6ACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxAC4AMQAuADkAIABNAGEAbgB1AHIAZQAgAEEAcABwAGwAaQBlAGQAIAB0AG8AIABTAG8AaQBsAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ATQBOAFMAbwBpAGwAXwBzAGMAbwBwAGUAMQBcAG4AawBnACAATgBcAG4ATQBOAFMAbwBpAGwAXwB7AHMAYwBvAHAAZQAxAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAPQAyACwAMwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyACwAMwB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyACwAMwB9ACkAKQBcAFwAdABpAG0AZQBzACAAUABGAFwAbgBNAE4AXwBqAG0AVAAyADMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABzAGUAYwBvAG4AZABhAHIAeQAgAGEAbgBkACAAdABlAHIAdABpAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgAHMAdABhAGcAZQBzACAAYQBzACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAbwByACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAG0AVAAyADMAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4ARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABmAG8AcgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAFAARgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAGYAZQBlAGQAbABvAHQAIABiAG8AdQBuAGQAYQByAHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUADIAMwAsACAARQBGAF8AbQBUADIAMwAsACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwAsACAAUABGACwAXABuACAAIAAgACAAKABNAE4AXwBqAG0AVAAyADMAIAAqACAAKAAxACAALQAgAEUARgBfAG0AVAAyADMAIAAtACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwApACkAIAAqACAAUABGAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADkALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAA9ADIALAAzAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIALAAzAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIALAAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADIAMwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABzAGUAYwBvAG4AZABhAHIAeQAgAGEAbgBkACAAdABlAHIAdABpAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgAHMAdABhAGcAZQBzACAAYQBzACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAbwByACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0AVAAyADMAXAAiACwAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABGAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAGYAZQBlAGQAbABvAHQAIABiAG8AdQBuAGQAYQByAHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAzAFwAbgBrAGcAIABOAFwAbgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAA9ADIALAAzAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIALAAzAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIALAAzAH0AKQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AUABGACkAXABuAE0ATgBfAGoAbQBUADIAMwAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAA6ACAAawBnACAATgBcAG4ARQBGAF8AbQBUADIAMwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4AUABGACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMgAzACwAIABFAEYAXwBtAFQAMgAzACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACwAIABQAEYALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAbQBUADIAMwAgACoAIAAoADEAIAAtACAARQBGAF8AbQBUADIAMwAgAC0AIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACkAKQAgACoAIAAoADEAIAAtACAAUABGACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AOQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAD0AMgAsADMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgAsADMAfQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAD0AMgAsADMAfQApACkAXABcAHQAaQBtAGUAcwAoADEALQBQAEYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMgAzAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbQBUADIAMwBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQA6ACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxAC4AMQAuADUAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABBAHQAbQBvAHMAcABoAGUAcgBpAGMAIABEAGUAcABvAHMAaQB0AGkAbwBuACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAEUAXwBOADIATwBhAGQAXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8ALABhAGQAfQA9ACgATQBNAFMAXwB7AEEAVABNAE8AUwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAE0ATQBTAF8AQQBUAE0ATwBTACAAPQAgAG0AYQBzAHMAIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAE4AMgBPACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgADoAIAByAGEAdABpAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE0AUwBfAEEAVABNAE8AUwAsACAARQBGAF8ATgAyAE8ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgACgATQBNAFMAXwBBAFQATQBPAFMAIAAqACAARQBGAF8ATgAyAE8AIAAqACAAQwBfAE4AMgBPACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAGEAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgA1ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPACwAYQBkAH0APQAoAE0ATQBTAF8AewBBAFQATQBPAFMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AQQBUAE0ATwBTAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBOADIATwBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgADoAIAByAGEAdABpAG8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBcACIALAAgAFwAIgByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABcAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkACAAbgBpAHQAcgBvAGcAZQBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcAG4ATQBNAFMAXwBBAFQATQBPAFMAXABuAGsAZwAgAE4AXABuAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAE0ATQBTACAAKABlAHgAYwBsAHUAZABpAG4AZwAgAE0ATgBfAGkAagBtADEAMwBUADIAKQAgADoAIABrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQALABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAgACoAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAG4AaQB0AHIAbwBnAGUAbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgA1ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBfAHsAQQBUAE0ATwBTAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAE0ATQBTACAAKABlAHgAYwBsAHUAZABpAG4AZwAgAE0ATgBfAGkAagBtADEAMwBUADIAKQAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4AMwAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAEQAaQByAGUAYwB0ACAATgAyAE8AIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AcwBcAG4ARQBfAE4AMgBPAGQAaQByAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAZABpAHIAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGoAbQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAbgBNAE4AXwBqAG0AVAAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAA6ACAAawBnACAATgBcAG4ARQBGAF8AagBtACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4AQwBfAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAA6ACAAcgBhAHQAaQBvAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQALAAgAEUARgBfAGoAbQAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAE0ATgBfAGoAbQBUACwAIABFAEYAXwBqAG0ALAAgAEMAXwBOADIATwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAGQAaQByAGUAYwB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBkAGkAcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPACwAZABpAHIAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGoAbQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AagBtAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgADoAIAByAGEAdABpAG8AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXABuAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAbgBNAE4AXwBqAG0ANQBUADEAXABuAGsAZwAgAE4AXABuAE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQA9ADUALABUAD0AMQB9AFwAbgBBAEUAXwBqACAAPQAgAHQAbwB0AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABrAGcAIABOAFwAbgBNAE0AUwBfAGoAbQA1AFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEARQBfAGoALAAgAE0ATQBTAF8AagBtADUAVAAxACwAXABuACAAIAAgACAAQQBFAF8AagAgACoAIABNAE0AUwBfAGoAbQA1AFQAMQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAbQA1AFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARQBfAGoAXAAiACwAXAAiAHQAbwB0AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQA1AFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFwAbgBBAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAZgByAG8AbQAgAGUAYQBjAGgAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAXABuAEEARQBfAGoAXABuAGsAZwAgAE4AXABuAEEARQBfAHsAagB9AD0ATgBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABOAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABoAGUAYQBkAFwAbgBOAEUAXwBqACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAOgAgAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAEQAXwBqACAAPQAgAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABkAGEAeQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoALAAgAE4ARQBfAGoALAAgAEQAXwBqACwAXABuACAAIAAgACAATgBfAGoAIAAqACAATgBFAF8AagAgACoAIABEAF8AagBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABmAHIAbwBtACAAZQBhAGMAaAAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBFAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXwB7AGoAfQA9AE4AXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATgBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAaABlAGEAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBFAF8AagBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIAA6ACAAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAXAAiACwAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABkAGEAeQBzAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABcAG4ATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABwAGUAcgAgAGgAZQBhAGQAIABwAGUAcgAgAGQAYQB5AFwAbgBOAEUAXwBqAFwAbgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBOAEUAXwB7AGoAfQA9AE4ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ATgBSAF8AewBqAH0AKQBcAG4ATgBJAF8AagAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABpAG4AdABhAGsAZQAgADoAIABrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBOAFIAXwBqACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHIAZQB0AGUAbgB0AGkAbwBuACAAZQB4AHAAcgBlAHMAcwBlAGQAIABhAHMAIABhACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAaQBuAHQAYQBrAGUAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAEkAXwBqACwAIABOAFIAXwBqACwAXABuACAAIAAgACAATgBJAF8AagAgACoAIAAoADEAIAAtACAATgBSAF8AagApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgAHAAZQByACAAaABlAGEAZAAgAHAAZQByACAAZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBFAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBfAHsAagB9AD0ATgBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAoADEALQBOAFIAXwB7AGoAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBJAF8AagBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuAHQAYQBrAGUAIAA6ACAAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBSAF8AagBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAcgBlAHQAZQBuAHQAaQBvAG4AIABlAHgAcAByAGUAcwBzAGUAZAAgAGEAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABpAG4AdABhAGsAZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuAHQAYQBrAGUAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAXABuAE4ASQBfAGoAXABuAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4ASQBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABDAFAAXwB7AGoAfQBcAFwAZABpAHYAIAA2AC4AMgA1AFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBDAFAAXwBqACAAPQAgAGMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuADYALgAyADUAIAA9ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHYAZQByAHQAaQBuAGcAIABjAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAaQBuAHQAbwAgAG4AaQB0AHIAbwBnAGUAbgAgADoAIAByAGEAdABpAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAF8AagAsACAAQwBQAF8AagAsAFwAbgAgACAAIAAgAEkAXwBqACAAKgAgAEMAUABfAGoAIAAvACAANgAuADIANQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgB0AGEAawBlACAAbwBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEkAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ASQBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABDAFAAXwB7AGoAfQBcAFwAZABpAHYAIAA2AC4AMgA1AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAXwBqAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAFAAXwBqAFwAIgAsAFwAIgBjAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AC4AMgA1AFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdgBlAHIAdABpAG4AZwAgAGMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABpAG4AdABvACAAbgBpAHQAcgBvAGcAZQBuACAAOgAgAHIAYQB0AGkAbwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE0ATgBfAGoAbQBUADIAXABuAGsAZwAgAE4AXABuAE0ATgBfAHsAagBtACwAVAA9ADIAfQA9AE4AVABfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXABuAE4AVABfAGoAbQBUADIAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAcwBlAGMAbwBuAGQAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAFQAXwBqAG0AVAAyACwAIABNAE0AUwBfAGoAbQBUADIALABcAG4AIAAgACAAIABOAFQAXwBqAG0AVAAyACAAKgAgAE0ATQBTAF8AagBtAFQAMgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtACwAVAA9ADIAfQA9AE4AVABfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABfAGoAbQBUADIAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQBUADIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBcAG4ATgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE4AVABfAGoAbQBUADIAXABuAGsAZwAgAE4AXABuAE4AVABfAHsAagBtACwAVAA9ADIAfQA9ACgATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQA9ADUAfQAtAEUARgBfAHsAbQA9ADUAfQApACkALQBNAE4AXwB7AGoAbQAsAFQAPQAzAH0AXABuAE0ATgBfAGoAbQA1AFQAMQAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgADoAIABrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtADUAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ARQBGAF8AbQA1ACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZABlAHAAbwBzAGkAdABlAGQAXABuAE0ATgBfAGoAbQBUADMAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIAA6ACAAawBnACAATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtADUAVAAxACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtADUALAAgAEUARgBfAG0ANQAsACAATQBOAF8AagBtAFQAMwAsAFwAbgAgACAAIAAgACgATQBOAF8AagBtADUAVAAxACAAKgAgACgAMQAgAC0AIABGAHIAYQBjAEcAQQBTAE0AXwBtADUAIAAtACAARQBGAF8AbQA1ACkAKQAgAC0AIABNAE4AXwBqAG0AVAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAFQAXwBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA3ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBUAF8AewBqAG0ALABUAD0AMgB9AD0AKABNAE4AXwB7AGoAbQA9ADUALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAD0ANQB9AC0ARQBGAF8AewBtAD0ANQB9ACkAKQAtAE0ATgBfAHsAagBtACwAVAA9ADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQA1AFQAMQBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AbQA1AFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtADUAXAAiACwAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZABlAHAAbwBzAGkAdABlAGQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAAOgAgAGsAZwAgAE4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXABuAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgAE0ATQBTAFwAbgBNAE4AXwBqAG0AMQBUADMAXABuAGsAZwAgAE4AXABuAE0ATgBfAHsAagBtAD0AMQAsAFQAPQAzAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQA9ADEALABUAD0AMwB9AFwAbgBBAEUAXwBqACAAPQAgAHQAbwB0AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABrAGcAIABOAFwAbgBNAE0AUwBfAGoAbQAxAFQAMwAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFAF8AagAsACAATQBNAFMAXwBqAG0AMQBUADMALABcAG4AIAAgACAAIABBAEUAXwBqACAAKgAgAE0ATQBTAF8AagBtADEAVAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtADEAVAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAOAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwB7AGoAbQA9ADEALABUAD0AMwB9AD0AQQBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0APQAxACwAVAA9ADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAF8AagBcACIALABcACIAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtADEAVAAzAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAxAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAyAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAzAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBlAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -28098,11 +29955,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMATABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA1ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AG8AIABlAGEAYwBoACAAdABlAHIAdABpAGEAcgB5ACAAcwB5AHMAdABlAG0AIABhAHMAcwB1AG0AZQBkACAAdABoAGEAdAAgADIAIABwAGUAcgAgAGMAZQBuAHQAIABpAHMAIAByAHUAbgAgAC0AIABvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAZQBlAGQAIABwAGEAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AG8AIABlAGEAYwBoACAAdABlAHIAdABpAGEAcgB5ACAAcwB5AHMAdABlAG0AIABhAHMAcwB1AG0AZQBkACAAdABoAGEAdAAgADIAIABwAGUAcgAgAGMAZQBuAHQAIABpAHMAIAByAHUAbgAgAC0AIABvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAZQBlAGQAIABwAGEAZAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AFwAbgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMQA2ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMQA5ACkAOwBcAG4AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAxAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADIATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAE0ATQBTAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMwBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABtAGkAZAAgAGYAZQBkAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAeABwAG8AcgB0ACAAbABvAG4AZwAgAGYAZQBkAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAxADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADEAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIATABlAG4AZwB0AGgAIABvAGYAIABTAHQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIAMQAtADgAMAAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIAOAAxAC0AMgAwADAAIABkAGEAeQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIAMgAwADEAKwAgAGQAYQB5AHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADIAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAyADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAHYAZQBkACAAZgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAcwAgAHQAbwAgAGEAIABzAGUAcABhAHIAYQB0AGUAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBhAG0AZQBkACAAXAB1ADAAMAAyADcAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAAtACAAbwByAGkAZwBpAG4AYQBsACAAaABhAHMAIABoAGUAYQBkAGUAcgAgAFwAdQAwADAAMgA3AFUAbgBpAHQAXAB1ADAAMAAyADcAIAB3AGgAaQBjAGgAIABjAG8AdgBlAHIAcwAgAHQAdwBvACAAYwBvAGwAdQBtAG4AcwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADAALAAgADcALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBlAGQAbABvAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBcACIALAAgAFwAIgBVAG4AaQB0AFwAIgAsACAAXAAiADIAMAAwADUALQAyADAAMAA5AFwAIgAsACAAXAAiADIAMAAxADAALQAyADAAMQA0AFwAIgAsACAAXAAiADIAMAAxADUALQAyADAAMQA5AFwAIgAsACAAXAAiADIAMAAyADAALQAyADAAMgAzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADcAMAAsACAANwAwACwAIAA3ADAALAAgADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAMQAwAC4AMAAsACAAMQAwAC4AMAAsACAAMQAwAC4ANAAsACAAMQAwAC4ANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAAMgAxAC4AMQAsACAAMgAwAC4ANAAsACAAMgAwAC4ANAAsACAAMgAwAC4ANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAAxADEANQAsACAAMQAxADUALAAgADEAMgAwACwAIAAxADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBkAGEAeQBcACIALAAgADEAMQAuADIALAAgADEAMAAuADgALAAgADEAMAAuADgALAAgADEAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBOACAAcgBlAHQAZQBuAHQAaQBvAG4AXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0ACAAbwBmACAAaQBuAHQAYQBrAGUAXAAiACwAIAAxADIALgA1ACwAIAAxADIALgA3ACwAIAAxADIALgA3ACwAIAAxADIALgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAMgA1ADAALAAgADIANQAwACwAIAAyADUAMAAsACAAMgA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBkAGEAeQBcACIALAAgADkALgAwACwAIAA4AC4ANQAsACAAOAAuADIALAAgADgALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgBOACAAcgBlAHQAZQBuAHQAaQBvAG4AXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0ACAAbwBmACAAaQBuAHQAYQBrAGUAXAAiACwAIAA2AC4ANgAsACAANwAuADAALAAgADcALgAwACwAIAA3AC4AMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADMAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARABpAGUAdAAgAHAAcgBvAHAAZQByAHQAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARABpAGUAdAAgAHAAcgBvAHAAZQByAHQAaQBlAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADMAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARABpAGUAdAAgAHAAcgBvAHAAZQByAHQAaQBlAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuACAAYwBvAGwAdQBtAG4AIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAZQBkACAATgBEAEYAIABhAG4AZAAgAEUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbwB2AGUAZAAgAGYAZQBlAGQAbABvAHQAIAB0AHkAcABlAHMAIAB0AG8AIABhACAAcwBlAHAAYQByAGEAdABlACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADMALAAgADgALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBlAGQAbABvAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAE4AdQB0AHIAaQBlAG4AdAAgAGEAbgBhAGwAeQBzAGkAcwBcACIALAAgAFwAIgBVAG4AaQB0AFwAIgAsACAAXAAiADIAMAAwADUALQAyADAAMAA5AFwAIgAsACAAXAAiADIAMAAxADAALQAyADAAMQA0AFwAIgAsACAAXAAiADIAMAAxADUALQAyADAAMQA5AFwAIgAsACAAXAAiADIAMAAyADAALQAyADAAMgAzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADMALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADQALgA1ACwAIAA0AC4ANQAsACAANAAuADgALAAgADQALgA4ACwAIAAwAC4AMAA0ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA1AC4AMAAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAE4ARABGAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADAALgAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4ANQAsACAANQAuADUALAAgADAALgAwADUANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABNAEMARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANAA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAATgBTAFcAIAB2AGEAbAB1AGUAcwAgAGYAbwByACAAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAE4AVAAgAGEAbgBkACAAVABBAFMAIABjAG8AbAB1AG0AbgBzACAAdwBpAHQAaAAgAFwAdQAwADAAMgA3AG4AbwAgAGQAYQB0AGEAXAB1ADAAMAAyADcAIAB2AGEAbAB1AGUAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMQAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAzACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlACAAKABTAHQAbwBjAGsAcABpAGwAZQApAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACkAXAAiACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA3ACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADUAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAKABFAEYAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AVAAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAwADUANAAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADAANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABQAG8AbgBkACkAXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEYAcgBhAGMARwBBAFMATQBtAFQAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgA2ACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlACAAKABTAHQAbwBjAGsAcABpAGwAZQApAFwAIgAsACAAMAAuADIANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4ANAAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADMANQAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEAOgAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAATQBlAHQAaABhAG4AZQAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgB7AEUAfQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgARABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAEQAXwBqACAAPQAgAGwAZQBuAGcAdABoACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABkAGEAeQBzAFwAbgBNAF8AagBtAFQAIAA9ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAaABlAGEAZABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABfAGoALAAgAE0AXwBqAG0AVAAsACAATgBfAGoALABcAG4AIAAgACAAIAAoAEQAXwBqACAAKgAgAE0AXwBqAG0AVAAgACoAIABOAF8AagApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABEAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAE4AXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqAFwAIgAsAFwAIgBsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAbQBUAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHAAZQByACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALABcACIAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAaABlAGEAZABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AFwAbgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAbgBNAF8AagBtADUAVAAxAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAagBtAD0ANQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAbQA9ADUALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAD0ANQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBfAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAF8AbQA1AFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAEMARgBfAGkAbQA1ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAGQAcgB5AGwAbwB0ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAXwBqACwAIABCAE8ALAAgAE0ATQBTAF8AbQA1AFQAMQAsACAATQBDAEYAXwBpAG0ANQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIABNAEMARgBfAGkAbQA1ACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAEMARgBfAGkAbQA1ACkALAAgAE0AQwBGAF8AaQBtADUALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABWAFMAXwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBfAG0ANQBUADEAIAAqACAATQBDAEYAXwBpAG0ANQAgACoAIAByAGgAbwBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAbQA1AFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAagBtAD0ANQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAbQA9ADUALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAD0ANQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAG0ANQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtADUAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAGQAcgB5AGwAbwB0ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAbgBNAF8AagBtAFQAMgBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAbQBUAD0AMgB9AD0AKAAxAC0AVgBTAEwAKQBcAFwAdABpAG0AZQBzACAAVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBMACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AVgBTAF8AagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAXwBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAXwBpAG0AIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgAGEAbgBkACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMATAAsACAAVgBTAF8AagAsACAAQgBPACwAIABNAE0AUwBfAG0AVAAyACwAIABNAEMARgBfAGkAbQAsACAAcgBoAG8ALABcAG4AIAAgACAAIAAoADEAIAAtACAAVgBTAEwAKQAgACoAIABWAFMAXwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBfAG0AVAAyACAAKgAgAE0AQwBGAF8AaQBtACAAKgAgAHIAaABvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQBUAD0AMgB9AD0AKAAxAC0AVgBTAEwAKQBcAFwAdABpAG0AZQBzACAAVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAEwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAXwBpAG0AXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIABNAE0AUwBcAG4ATQBfAGoAbQAxAFQAMwBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAbQA9ADEALABUAD0AMwB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQAxACwAVAA9ADMAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADEAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAXwBqACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBfAG0AMQBUADMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIAB0AGUAcgB0AGkAYQByAHkAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAEMARgBfAGkAbQAxACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAHIAaABvACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFYAUwBfAGoALAAgAEIATwAsACAATQBNAFMAXwBtADEAVAAzACwAIABNAEMARgBfAGkAbQAxACwAIAByAGgAbwAsAFwAbgAgACAAIAAgAFYAUwBfAGoAIAAqACAAQgBPACAAKgAgAE0ATQBTAF8AbQAxAFQAMwAgACoAIABNAEMARgBfAGkAbQAxACAAKgAgAHIAaABvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAbQAxAFQAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAagBtAD0AMQAsAFQAPQAzAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAbQA9ADEALABUAD0AMwB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAagAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtADEAVAAzAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtADEAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFYAUwBfAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AVgBTAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAoADEALQBEAE0ARABfAHsAagB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBBACkAXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAEQATQBEAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAEEAIAA9ACAAYQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALAAgAEQATQBEAF8AagAsACAAQQAsAFwAbgAgACAAIAAgAEkAXwBqACAAKgAgACgAMQAgAC0AIABEAE0ARABfAGoAKQAgACoAIAAoADEAIAAtACAAQQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARABNAEQAXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AQQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAXwBqAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIABqACAAOgAgAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAEQAXwBqAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgAGoAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAFwAIgAsAFwAIgBhAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4AOQAgAE0AYQBuAHUAcgBlACAAQQBwAHAAbABpAGUAZAAgAHQAbwAgAFMAbwBpAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAbgBrAGcAIABOAFwAbgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAA9ADIALAAzAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIALAAzAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIALAAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXABuAE0ATgBfAGoAbQBUADIAMwAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAA6ACAAawBnACAATgBcAG4ARQBGAF8AbQBUADIAMwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4AUABGACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMgAzACwAIABFAEYAXwBtAFQAMgAzACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACwAIABQAEYALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAbQBUADIAMwAgACoAIAAoADEAIAAtACAARQBGAF8AbQBUADIAMwAgAC0AIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACkAKQAgACoAIABQAEYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AOQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMQB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAD0AMgAsADMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgAsADMAfQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAD0AMgAsADMAfQApACkAXABcAHQAaQBtAGUAcwAgAFAARgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMgAzAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbQBUADIAMwBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADMAXABuAGsAZwAgAE4AXABuAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAD0AMgAsADMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgAsADMAfQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAD0AMgAsADMAfQApACkAXABcAHQAaQBtAGUAcwAoADEALQBQAEYAKQBcAG4ATQBOAF8AagBtAFQAMgAzACAAPQAgAG0AYQBzAHMAIABvAGYAIABOACAAaQBuACAAcwBlAGMAbwBuAGQAYQByAHkAIABhAG4AZAAgAHQAZQByAHQAaQBhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIABzAHQAYQBnAGUAcwAgAGEAcwAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgADoAIABrAGcAIABOAFwAbgBFAEYAXwBtAFQAMgAzACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAbgBQAEYAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABmAGUAZQBkAGwAbwB0ACAAYgBvAHUAbgBkAGEAcgB5ACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAyADMALAAgAEUARgBfAG0AVAAyADMALAAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMALAAgAFAARgAsAFwAbgAgACAAIAAgACgATQBOAF8AagBtAFQAMgAzACAAKgAgACgAMQAgAC0AIABFAEYAXwBtAFQAMgAzACAALQAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMAKQApACAAKgAgACgAMQAgAC0AIABQAEYAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwBzAGMAbwBwAGUAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgA5ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAXwB7AHMAYwBvAHAAZQAzAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAPQAyACwAMwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyACwAMwB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyACwAMwB9ACkAKQBcAFwAdABpAG0AZQBzACgAMQAtAFAARgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVAAyADMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAaQBuACAAcwBlAGMAbwBuAGQAYQByAHkAIABhAG4AZAAgAHQAZQByAHQAaQBhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIABzAHQAYQBnAGUAcwAgAGEAcwAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFQAMgAzAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABmAG8AcgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAARgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABmAGUAZQBkAGwAbwB0ACAAYgBvAHUAbgBkAGEAcgB5ACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4ANQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAEEAdABtAG8AcwBwAGgAZQByAGkAYwAgAEQAZQBwAG8AcwBpAHQAaQBvAG4AIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcAG4ARQBfAE4AMgBPAGEAZABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGEAZAB9AD0AKABNAE0AUwBfAHsAQQBUAE0ATwBTAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ATQBNAFMAXwBBAFQATQBPAFMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4ARQBGAF8ATgAyAE8AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAF8AQQBUAE0ATwBTACwAIABFAEYAXwBOADIATwAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAE0AUwBfAEEAVABNAE8AUwAgACoAIABFAEYAXwBOADIATwAgACoAIABDAF8ATgAyAE8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AYQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABhAGQAfQA9ACgATQBNAFMAXwB7AEEAVABNAE8AUwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsACAAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAIABuAGkAdAByAG8AZwBlAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBNAE0AUwBfAEEAVABNAE8AUwBcAG4AawBnACAATgBcAG4ATQBNAFMAXwB7AEEAVABNAE8AUwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAH0AKQBcAG4ATQBOAF8AagBtAFQAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAATQBOAF8AaQBqAG0AMQAzAFQAMgApACAAOgAgAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0AVAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQALAAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACAAKgAgAEYAcgBhAGMARwBBAFMATQBfAG0AVABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBvAGwAYQB0AGkAbABpAHMAZQBkACAAbgBpAHQAcgBvAGcAZQBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBfAEEAVABNAE8AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVABcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAATQBOAF8AaQBqAG0AMQAzAFQAMgApACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEAOgAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQAuADEALgAzACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAARABpAHIAZQBjAHQAIABOADIATwAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBzAFwAbgBFAF8ATgAyAE8AZABpAHIAXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAALAAgAE0ATQBTACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABOAFwAbgBFAEYAXwBqAG0AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBDAF8ATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgADoAIAByAGEAdABpAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAsACAARQBGAF8AagBtACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgATQBOAF8AagBtAFQALAAgAEUARgBfAGoAbQAsACAAQwBfAE4AMgBPACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAGQAaQByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABkAGkAcgB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAagBtAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHAAZQByACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAALAAgAE0ATQBTACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBqAG0AXAAiACwAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0ATgBfAGoAbQA1AFQAMQBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABuAEEARQBfAGoAIAA9ACAAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtADUAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFAF8AagAsACAATQBNAFMAXwBqAG0ANQBUADEALABcAG4AIAAgACAAIABBAEUAXwBqACAAKgAgAE0ATQBTAF8AagBtADUAVAAxAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtADUAVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AQQBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAF8AagBcACIALABcACIAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtADUAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXABuAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABmAHIAbwBtACAAZQBhAGMAaAAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcABcAG4AQQBFAF8AagBcAG4AawBnACAATgBcAG4AQQBFAF8AewBqAH0APQBOAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE4ARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAH0AXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGgAZQBhAGQAXABuAE4ARQBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIAA6ACAAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcAG4ARABfAGoAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGQAYQB5AHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATgBFAF8AagAsACAARABfAGoALABcAG4AIAAgACAAIABOAF8AagAgACoAIABOAEUAXwBqACAAKgAgAEQAXwBqAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgAGYAcgBvAG0AIABlAGEAYwBoACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEARQBfAHsAagB9AD0ATgBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABOAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABoAGUAYQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEUAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgADoAIABrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGQAYQB5AHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAFwAbgBOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgAHAAZQByACAAaABlAGEAZAAgAHAAZQByACAAZABhAHkAXABuAE4ARQBfAGoAXABuAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4ARQBfAHsAagB9AD0ATgBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAoADEALQBOAFIAXwB7AGoAfQApAFwAbgBOAEkAXwBqACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgB0AGEAawBlACAAOgAgAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4AUgBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcgBlAHQAZQBuAHQAaQBvAG4AIABlAHgAcAByAGUAcwBzAGUAZAAgAGEAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABpAG4AdABhAGsAZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4ASQBfAGoALAAgAE4AUgBfAGoALABcAG4AIAAgACAAIABOAEkAXwBqACAAKgAgACgAMQAgAC0AIABOAFIAXwBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAcABlAHIAIABoAGUAYQBkACAAcABlAHIAIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBFAF8AewBqAH0APQBOAEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAE4AUgBfAHsAagB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEkAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABpAG4AdABhAGsAZQAgADoAIABrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFIAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIAByAGUAdABlAG4AdABpAG8AbgAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgB0AGEAawBlACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AdABhAGsAZQAgAG8AZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQBcAG4ATgBJAF8AagBcAG4AawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBJAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEMAUABfAHsAagB9AFwAXABkAGkAdgAgADYALgAyADUAXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAEMAUABfAGoAIAA9ACAAYwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ANgAuADIANQAgAD0AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdgBlAHIAdABpAG4AZwAgAGMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABpAG4AdABvACAAbgBpAHQAcgBvAGcAZQBuACAAOgAgAHIAYQB0AGkAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABDAFAAXwBqACwAXABuACAAIAAgACAASQBfAGoAIAAqACAAQwBQAF8AagAgAC8AIAA2AC4AMgA1AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuAHQAYQBrAGUAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBJAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEMAUABfAHsAagB9AFwAXABkAGkAdgAgADYALgAyADUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAUABfAGoAXAAiACwAXAAiAGMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADYALgAyADUAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB2AGUAcgB0AGkAbgBnACAAYwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGkAbgB0AG8AIABuAGkAdAByAG8AZwBlAG4AIAA6ACAAcgBhAHQAaQBvAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBOAF8AagBtAFQAMgBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0ALABUAD0AMgB9AD0ATgBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAG4ATgBUAF8AagBtAFQAMgAgAD0AIABuAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIABzAGUAYwBvAG4AZABhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4ATQBNAFMAXwBqAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AVABfAGoAbQBUADIALAAgAE0ATQBTAF8AagBtAFQAMgAsAFwAbgAgACAAIAAgAE4AVABfAGoAbQBUADIAIAAqACAATQBNAFMAXwBqAG0AVAAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtAFQAMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AewBqAG0ALABUAD0AMgB9AD0ATgBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAF8AagBtAFQAMgBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAcwBlAGMAbwBuAGQAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAFwAbgBOAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATgBUAF8AagBtAFQAMgBcAG4AawBnACAATgBcAG4ATgBUAF8AewBqAG0ALABUAD0AMgB9AD0AKABNAE4AXwB7AGoAbQA9ADUALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAD0ANQB9AC0ARQBGAF8AewBtAD0ANQB9ACkAKQAtAE0ATgBfAHsAagBtACwAVAA9ADMAfQBcAG4ATQBOAF8AagBtADUAVAAxACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAAOgAgAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0ANQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBFAEYAXwBtADUAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABkAGUAcABvAHMAaQB0AGUAZABcAG4ATQBOAF8AagBtAFQAMwAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgADoAIABrAGcAIABOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AXwBqAG0ANQBUADEALAAgAEYAcgBhAGMARwBBAFMATQBfAG0ANQAsACAARQBGAF8AbQA1ACwAIABNAE4AXwBqAG0AVAAzACwAXABuACAAIAAgACAAKABNAE4AXwBqAG0ANQBUADEAIAAqACAAKAAxACAALQAgAEYAcgBhAGMARwBBAFMATQBfAG0ANQAgAC0AIABFAEYAXwBtADUAKQApACAALQAgAE0ATgBfAGoAbQBUADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AVABfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADcAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAFQAXwB7AGoAbQAsAFQAPQAyAH0APQAoAE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0APQA1AH0ALQBFAEYAXwB7AG0APQA1AH0AKQApAC0ATQBOAF8AewBqAG0ALABUAD0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtADUAVAAxAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABpAG4AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtADUAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0ANQBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABkAGUAcABvAHMAaQB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIAA6ACAAawBnACAATgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXABuAE0ATgBfAGoAbQAxAFQAMwBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0APQAxACwAVAA9ADMAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtAD0AMQAsAFQAPQAzAH0AXABuAEEARQBfAGoAIAA9ACAAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtADEAVAAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAEUAXwBqACwAIABNAE0AUwBfAGoAbQAxAFQAMwAsAFwAbgAgACAAIAAgAEEARQBfAGoAIAAqACAATQBNAFMAXwBqAG0AMQBUADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwBqAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA4ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtAD0AMQAsAFQAPQAzAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQA9ADEALABUAD0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEUAXwBqAFwAIgAsAFwAIgB0AG8AdABhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABiAHkAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBqAG0AMQBUADMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADIATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADMATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAGUAcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBEAGEAdABhACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -28297,16 +30159,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -28317,15 +30178,15 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28342,12 +30203,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>